--- a/content/Question Bank/Coding Questions/Unit 11 - File Handling/Unit 11 - File Handling - Coding Questions.xlsx
+++ b/content/Question Bank/Coding Questions/Unit 11 - File Handling/Unit 11 - File Handling - Coding Questions.xlsx
@@ -596,13 +596,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Imagine reading a text file. Read all the lines from input and print how many lines there are.
+          <t xml:space="preserve">
+Riya is the secretary of her hostel's cultural committee, and the warden hands her a plain text file of announcements — one announcement per line. Before printing notices, she wants a quick check of how many announcements the file holds. Write a program that reads all the lines given as input (treat them as the file's contents) and prints the number of lines.
 ### Input Format
-- All lines: the file contents
+- All lines: the file contents (each line is one announcement)
 ### Output Format
 ```
 3
 ```
+### Example Walkthrough
+The sample input has three lines: `a`, `b`, and `c`. Reading them one by one, the count goes 1, 2, 3. Since there are 3 lines in total, the program prints `3`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -744,13 +747,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Read one line of comma-separated values using the csv module and print how many fields it contains.
+          <t xml:space="preserve">
+The canteen at Arjun's college exports its daily sales as CSV (comma-separated values), where each row is a list of entries separated by commas. Before processing a row, Arjun wants to know how many entries it contains. Write a program that reads one CSV row using Python's csv module and prints how many fields (comma-separated pieces) it has.
 ### Input Format
 - Line 1: A CSV row
 ### Output Format
 ```
 3
 ```
+### Example Walkthrough
+The sample row is `a,b,c`. Splitting it at the commas gives three fields — `a`, `b`, and `c` — so the program prints `3`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -889,13 +895,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Read one line of JSON describing an object and print the value of its 'name' field.
+          <t xml:space="preserve">
+The college fest website stores each participant's details as JSON, a text format made of `"key": value` pairs inside curly braces. Meera at the registration desk only needs each participant's name. Write a program that reads one line of JSON describing a person and prints the value stored under its 'name' field.
 ### Input Format
 - Line 1: A JSON object
 ### Output Format
 ```
 Asha
 ```
+### Example Walkthrough
+The sample input is `{"name": "Asha", "age": 20}`. Loading it with `json.loads` gives a dictionary, and looking up the `name` key returns `Asha`, which is printed.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1029,13 +1038,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Use pathlib to read a file name and print its extension, including the leading dot (for example '.txt').
+          <t xml:space="preserve">
+The librarian is digitising old question papers, and files arrive with all kinds of names — some end in .txt, some in .pdf, some in .docx. To sort them into folders she first needs each file's extension. Write a program that reads a file name and, using Python's pathlib module, prints its extension including the leading dot (for example '.txt').
 ### Input Format
 - Line 1: A file name
 ### Output Format
 ```
 .txt
 ```
+### Example Walkthrough
+For the sample name `file.txt`, pathlib's `Path('file.txt').suffix` looks at everything from the last dot onwards, which is `.txt`, so that is exactly what gets printed.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1163,7 +1175,8 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A CSV file has a header row 'name,score' followed by data rows. Use csv.DictReader to print the total of the 'score' column.
+          <t xml:space="preserve">
+Coach Nair records his cricket team's practice scores in a CSV file: a header row 'name,score' followed by one row per player. At the end of the session he wants the team's total. Write a program that reads the CSV using csv.DictReader and prints the total of the 'score' column.
 ### Input Format
 - Line 1: Header 'name,score'
 - Next lines: data rows
@@ -1171,6 +1184,8 @@
 ```
 170
 ```
+### Example Walkthrough
+The sample data rows are `asha,80` and `kabir,90`. DictReader turns each row into a dictionary using the header names as keys, so the program adds the score values 80 + 90 = 170 and prints `170`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1323,13 +1338,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Read one line of JSON containing a list of numbers and print their sum.
+          <t xml:space="preserve">
+Dev's mobile recharge app logs how much data he used each day as a JSON list of numbers, like `[1, 2, 3]`. He wants his total usage for the period in one shot. Write a program that reads one line containing a JSON list of numbers and prints their sum.
 ### Input Format
 - Line 1: A JSON list of numbers
 ### Output Format
 ```
 10
 ```
+### Example Walkthrough
+The sample input `[1, 2, 3, 4]` becomes a normal Python list after `json.loads`. Adding the values gives 1 + 2 + 3 + 4 = 10, so the program prints `10`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1468,7 +1486,8 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>A config file has N lines like 'key=value'. Read N, then the N lines, then a key to look up. Print the matching value, or 'Not Found'.
+          <t xml:space="preserve">
+The coding club is setting up its website, and all the settings live in a config file with lines like 'key=value' (for example 'port=8080'). Tanvi needs a quick way to look up any one setting. Write a program that reads N, then N 'key=value' lines, then a key to look up. Print the value stored for that key, or 'Not Found' if the key does not appear in the file.
 ### Input Format
 - Line 1: N
 - Next N lines: 'key=value'
@@ -1477,6 +1496,8 @@
 ```
 8080
 ```
+### Example Walkthrough
+N is 2, and the lines `host=localhost` and `port=8080` are each split at the '=' into a key and a value. The key to look up is `port`, which matches the second line, so the program prints `8080`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1636,7 +1657,8 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Read N records, each a name and an age separated by a space, and write them out as CSV rows 'name,age' using the csv module.
+          <t xml:space="preserve">
+For sports day, volunteers noted each participant on paper as a name and an age separated by a space. The events team now needs the same list as a CSV file to upload to the college portal. Write a program that reads N records of 'name age' and writes each one out as a CSV row 'name,age' using the csv module.
 ### Input Format
 - Line 1: N
 - Next N lines: 'name age'
@@ -1645,6 +1667,8 @@
 asha,20
 kabir,21
 ```
+### Example Walkthrough
+N is 2, so the program reads `asha 20` and `kabir 21`, splits each record at the space, and writes the two parts joined by a comma instead: first `asha,20`, then `kabir,21`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1797,7 +1821,8 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A log file has N lines, each starting with a level (INFO, WARN, or ERROR) followed by a message. Read N, then the lines, and print each level that appears with its count as 'LEVEL count', sorted alphabetically by level.
+          <t xml:space="preserve">
+The city bus-tracking app that Farhan helps maintain writes a log file where every line starts with a level — INFO, WARN, or ERROR — followed by a message. To spot trouble quickly, Farhan wants a count of each level. Write a program that reads N and then N log lines, and prints each level that appears with its count as 'LEVEL count', one per line, sorted alphabetically by level.
 ### Input Format
 - Line 1: N
 - Next N lines: 'LEVEL message'
@@ -1806,6 +1831,8 @@
 ERROR 1
 INFO 2
 ```
+### Example Walkthrough
+The 3 sample lines have the levels INFO, ERROR, INFO — so ERROR appears once and INFO twice. Sorted alphabetically, ERROR comes before INFO, giving `ERROR 1` on the first line and `INFO 2` on the second.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
@@ -1960,7 +1987,8 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A CSV has a header row followed by data rows. Convert the whole thing to a JSON list of objects (one object per data row) and print it with json.dumps.
+          <t xml:space="preserve">
+The alumni cell keeps member details in a CSV file — a header row followed by data rows — but the new college website needs the same data as JSON. Write a program that reads the CSV (first line is the header, remaining lines are data), turns each data row into an object using the header names as keys, and prints the whole list of objects with json.dumps. Every value stays a string, exactly as it appeared in the CSV.
 ### Input Format
 - Line 1: Header row
 - Next lines: data rows
@@ -1968,6 +1996,8 @@
 ```
 [{"name": "asha", "age": "20"}, {"name": "kabir", "age": "21"}]
 ```
+### Example Walkthrough
+The header `name,age` provides the keys. The row `asha,20` becomes the object {"name": "asha", "age": "20"}, and `kabir,21` becomes a similar object. json.dumps then prints both together as one JSON list.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>

--- a/content/Question Bank/Coding Questions/Unit 11 - File Handling/Unit 11 - File Handling - Coding Questions.xlsx
+++ b/content/Question Bank/Coding Questions/Unit 11 - File Handling/Unit 11 - File Handling - Coding Questions.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4051,9 +4051,9 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>A CSV has header 'name,m1,m2,m3' and data rows. Print a new CSV with header 'name,total,average', where average is rounded to 1 decimal place, one row per student.
+          <t>A CSV has header 'name,`m1`,`m2`,`m3`' and data rows. Print a new CSV with header 'name,total,average', where average is rounded to 1 decimal place, one row per student.
 ### Input Format
-- Line 1: Header 'name,m1,m2,m3'
+- Line 1: Header 'name,`m1`,`m2`,`m3`'
 - Next lines: data rows
 ### Output Format
 ```
@@ -5015,7 +5015,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Read a sentence and print a JSON object mapping each word to how many times it appears, with the keys sorted alphabetically. Use json.dumps with sort_keys.
+          <t>Read a sentence and print a JSON object mapping each word to how many times it appears, with the keys sorted alphabetically. Use json.dumps with `sort_keys`.
 ### Input Format
 - Line 1: A sentence
 ### Output Format

--- a/content/Question Bank/Coding Questions/Unit 11 - File Handling/Unit 11 - File Handling - Coding Questions.xlsx
+++ b/content/Question Bank/Coding Questions/Unit 11 - File Handling/Unit 11 - File Handling - Coding Questions.xlsx
@@ -7,7 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 4" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH31"/>
+  <dimension ref="A1:AH11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -621,12 +624,22 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -636,7 +649,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>text-processing</t>
+          <t>file-operations</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -772,12 +785,22 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -787,7 +810,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>csv</t>
+          <t>csv-processing</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -920,12 +943,22 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -935,7 +968,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>json-processing</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1063,12 +1096,22 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1078,7 +1121,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>text-processing</t>
+          <t>file-paths</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1201,12 +1244,22 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1216,7 +1269,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>csv</t>
+          <t>csv-processing</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1363,12 +1416,22 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1378,7 +1441,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>json-processing</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1513,12 +1576,22 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1528,7 +1601,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>text-processing</t>
+          <t>file-operations</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1684,12 +1757,22 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>python-fundamentals</t>
+          <t>python</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1699,7 +1782,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>csv</t>
+          <t>csv-processing</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1816,10 +1899,538 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Python - Line Counter</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Line Counter. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: N
+- Next N lines: Text
+### Output Format
+```
+3
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>file-handling</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>file-operations</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>3
+a
+b
+c</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>1
+hello</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>2
+blank</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>4
+one
+two
+three
+four</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>2
+A
+B</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>5
+1
+2
+3
+4
+5</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>n=int(input())
+for _ in range(n): input()
+print(n)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Python - Longest File Line</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Longest File Line. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: N
+- Next N lines: Text
+### Output Format
+```
+3
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>python - Set 1</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>file-handling</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>file-operations</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>3
+a
+abc
+ab</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1
+hello</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>2
+abc</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>3
+python
+java
+c</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>2
+long line
+x</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>4
+a
+bb
+ccc
+dddd</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>n=int(input()); best=0
+for _ in range(n): best=max(best,len(input()))
+print(best)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AH11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>explanation</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>difficulty</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>bloomTaxonomy</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>subjects</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>topics</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>subTopics</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>companies</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>codingType</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>supportAllLanguages</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>enablePartialScore</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ignoreCase</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>testcase1_input</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>testcase1_output</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>testcase2_input</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>testcase2_output</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>testcase3_input</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>testcase3_output</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>testcase4_input</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>testcase4_output</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>testcase5_input</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>testcase5_output</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>testcase6_input</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>testcase6_output</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>testcase7_input</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>testcase7_output</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>preloadCode_python</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>solution_python</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>hints</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
           <t>Python - Log Level Counts</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t xml:space="preserve">
 The city bus-tracking app that Farhan helps maintain writes a log file where every line starts with a level — INFO, WARN, or ERROR — followed by a message. To spot trouble quickly, Farhan wants a count of each level. Write a program that reads N and then N log lines, and prints each level that appears with its count as 'LEVEL count', one per line, sorted alphabetically by level.
@@ -1838,54 +2449,64 @@
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D2" t="n">
         <v>5</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>file-handling</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>text-processing</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>file-operations</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O10" t="b">
+      <c r="O2" t="b">
         <v>0</v>
       </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="b">
-        <v>1</v>
-      </c>
-      <c r="R10" t="inlineStr">
+      <c r="P2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="b">
+        <v>1</v>
+      </c>
+      <c r="R2" t="inlineStr">
         <is>
           <t>3
 INFO started
@@ -1893,52 +2514,52 @@
 INFO done</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>ERROR 1
 INFO 2</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>2
 WARN x
 WARN y</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>WARN 2</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>1
 ERROR z</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>ERROR 1</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>1
 INFO only</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>INFO 1</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>4
 ERROR a
@@ -1947,27 +2568,27 @@
 ERROR d</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>ERROR 2
 INFO 1
 WARN 1</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>2
 INFO x
 ERROR y</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>ERROR 1
 INFO 1</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>n = int(input())
 counts = {}
@@ -1979,13 +2600,13 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Python - CSV to JSON</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t xml:space="preserve">
 The alumni cell keeps member details in a CSV file — a header row followed by data rows — but the new college website needs the same data as JSON. Write a program that reads the CSV (first line is the header, remaining lines are data), turns each data row into an object using the header names as keys, and prints the whole list of objects with json.dumps. Every value stays a string, exactly as it appeared in the CSV.
@@ -2003,110 +2624,120 @@
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D3" t="n">
         <v>5</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>file-handling</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>json</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>csv-processing</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O11" t="b">
+      <c r="O3" t="b">
         <v>0</v>
       </c>
-      <c r="P11" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="b">
-        <v>1</v>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="P3" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="b">
+        <v>1</v>
+      </c>
+      <c r="R3" t="inlineStr">
         <is>
           <t>name,age
 asha,20
 kabir,21</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>[{"name": "asha", "age": "20"}, {"name": "kabir", "age": "21"}]</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>city
 Delhi</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>[{"city": "Delhi"}]</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>a,b
 1,2
 3,4</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>[{"a": "1", "b": "2"}, {"a": "3", "b": "4"}]</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>name,age</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>x,y,z
 1,2,3</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>[{"x": "1", "y": "2", "z": "3"}]</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>a
 b
@@ -2114,23 +2745,23 @@
 d</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>[{"a": "b"}, {"a": "c"}, {"a": "d"}]</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>col1,col2
 v1,v2</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>[{"col1": "v1", "col2": "v2"}]</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>import csv, json, sys
 rows = list(csv.DictReader(sys.stdin))
@@ -2138,13 +2769,13 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Python - Numbered Lines</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Read the lines of a file and print each one prefixed by its line number starting at 1, in the form 'number: line'.
 ### Input Format
@@ -2154,95 +2785,107 @@
 1: apple
 2: banana
 ```
+### Example Walkthrough
+In the sample, the lines are `apple` and `banana`. Prefixing each with its 1-based line number gives `1: apple` and `2: banana`, which the program prints.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D4" t="n">
         <v>5</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>file-handling</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>text-processing</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>file-operations</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O12" t="b">
+      <c r="O4" t="b">
         <v>0</v>
       </c>
-      <c r="P12" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q12" t="b">
-        <v>1</v>
-      </c>
-      <c r="R12" t="inlineStr">
+      <c r="P4" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="b">
+        <v>1</v>
+      </c>
+      <c r="R4" t="inlineStr">
         <is>
           <t>apple
 banana</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>1: apple
 2: banana</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>one</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>1: one</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>a
 b
 c</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>1: a
 2: b
 3: c</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>x
 y
@@ -2250,7 +2893,7 @@
 w</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>1: x
 2: y
@@ -2258,29 +2901,29 @@
 4: w</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>solo</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>1: solo</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>p
 q</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1: p
 2: q</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>m
 n
@@ -2289,7 +2932,7 @@
 q</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>1: m
 2: n
@@ -2298,7 +2941,7 @@
 5: q</t>
         </is>
       </c>
-      <c r="AG12" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>import sys
 for i, line in enumerate(sys.stdin.read().splitlines(), 1):
@@ -2306,13 +2949,13 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Python - Word Count of a File</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Read all lines of a file and print the total number of words across every line.
 ### Input Format
@@ -2321,101 +2964,113 @@
 ```
 4
 ```
+### Example Walkthrough
+In the sample, the lines are `the quick` and `brown fox`. Together they contain `4` words, so the program prints `4`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D5" t="n">
         <v>5</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>file-handling</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>text-processing</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>file-operations</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O13" t="b">
+      <c r="O5" t="b">
         <v>0</v>
       </c>
-      <c r="P13" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q13" t="b">
-        <v>1</v>
-      </c>
-      <c r="R13" t="inlineStr">
+      <c r="P5" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="b">
+        <v>1</v>
+      </c>
+      <c r="R5" t="inlineStr">
         <is>
           <t>the quick
 brown fox</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>hello</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>a b
 c d e</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>one</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>a
 b
@@ -2423,33 +3078,33 @@
 d</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t xml:space="preserve">  spaced   words  </t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AD13" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>x y z
 p q</t>
         </is>
       </c>
-      <c r="AE13" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AG13" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>import sys
 text = sys.stdin.read()
@@ -2457,13 +3112,13 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Python - File Name from Path</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Use pathlib to read a file path and print just the final file name.
 ### Input Format
@@ -2472,142 +3127,154 @@
 ```
 file.txt
 ```
+### Example Walkthrough
+In the sample, the path is `home/user/file.txt`. The final component is `file.txt`, which the program prints.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D6" t="n">
         <v>5</v>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>file-handling</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>text-processing</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>file-paths</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O14" t="b">
+      <c r="O6" t="b">
         <v>0</v>
       </c>
-      <c r="P14" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q14" t="b">
-        <v>1</v>
-      </c>
-      <c r="R14" t="inlineStr">
+      <c r="P6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="b">
+        <v>1</v>
+      </c>
+      <c r="R6" t="inlineStr">
         <is>
           <t>/home/user/file.txt</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>file.txt</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>docs/report.pdf</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>report.pdf</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>data.csv</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>data.csv</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>file.txt</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>file.txt</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>/a/b/c/d.py</t>
         </is>
       </c>
-      <c r="AA14" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>d.py</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>/trailing/slash/dir/</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>dir</t>
         </is>
       </c>
-      <c r="AD14" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>/x/y/z/report.final.csv</t>
         </is>
       </c>
-      <c r="AE14" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>report.final.csv</t>
         </is>
       </c>
-      <c r="AG14" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>from pathlib import PurePosixPath
 print(PurePosixPath(input()).name)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Python - Shout the File</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Read the lines of a file and print each line converted to upper case.
 ### Input Format
@@ -2617,125 +3284,137 @@
 HELLO
 WORLD
 ```
+### Example Walkthrough
+In the sample, the lines are `hello` and `world`. Converting each to upper case gives `HELLO` and `WORLD`, which the program prints one per line.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D7" t="n">
         <v>5</v>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>file-handling</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>text-processing</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>file-operations</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O15" t="b">
+      <c r="O7" t="b">
         <v>0</v>
       </c>
-      <c r="P15" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q15" t="b">
-        <v>1</v>
-      </c>
-      <c r="R15" t="inlineStr">
+      <c r="P7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="b">
+        <v>1</v>
+      </c>
+      <c r="R7" t="inlineStr">
         <is>
           <t>hello
 world</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>HELLO
 WORLD</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>abc</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>a
 b</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>A
 B</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>MiXeD case</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>MIXED CASE</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>already UPPER</t>
         </is>
       </c>
-      <c r="AA15" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>ALREADY UPPER</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>1 2 3
 four</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1 2 3
 FOUR</t>
         </is>
       </c>
-      <c r="AD15" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>x
 y
@@ -2743,7 +3422,7 @@
 w</t>
         </is>
       </c>
-      <c r="AE15" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>X
 Y
@@ -2751,7 +3430,7 @@
 W</t>
         </is>
       </c>
-      <c r="AG15" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>import sys
 for line in sys.stdin.read().splitlines():
@@ -2759,13 +3438,13 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Python - Character Count</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Read the lines of a file and print how many characters there are in total, not counting the line breaks.
 ### Input Format
@@ -2774,114 +3453,126 @@
 ```
 5
 ```
+### Example Walkthrough
+In the sample, the only line is `hello`, which has `5` characters, so the program prints `5`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D8" t="n">
         <v>5</v>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>file-handling</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>text-processing</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>file-operations</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O16" t="b">
+      <c r="O8" t="b">
         <v>0</v>
       </c>
-      <c r="P16" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q16" t="b">
-        <v>1</v>
-      </c>
-      <c r="R16" t="inlineStr">
+      <c r="P8" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="b">
+        <v>1</v>
+      </c>
+      <c r="R8" t="inlineStr">
         <is>
           <t>abc
 de</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>hello</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>a
 b
 c</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>ab
 cd
 ef</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>one
 two
@@ -2889,23 +3580,23 @@
 four</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="AD16" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t xml:space="preserve">  spaced  
 line</t>
         </is>
       </c>
-      <c r="AE16" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="AG16" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>import sys
 lines = sys.stdin.read().splitlines()
@@ -2913,13 +3604,13 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Python - Reverse the Lines</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Read the lines of a file and print them in reverse order (last line first).
 ### Input Format
@@ -2930,105 +3621,117 @@
 b
 a
 ```
+### Example Walkthrough
+In the sample, the lines are `a`, `b`, and `c`. Printed in reverse order, they become `c`, `b`, and `a`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D9" t="n">
         <v>5</v>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>file-handling</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>text-processing</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>file-operations</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O17" t="b">
+      <c r="O9" t="b">
         <v>0</v>
       </c>
-      <c r="P17" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q17" t="b">
-        <v>1</v>
-      </c>
-      <c r="R17" t="inlineStr">
+      <c r="P9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="b">
+        <v>1</v>
+      </c>
+      <c r="R9" t="inlineStr">
         <is>
           <t>a
 b
 c</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>c
 b
 a</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>one</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>one</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>x
 y</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y
 x</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>p
 q
@@ -3036,7 +3739,7 @@
 s</t>
         </is>
       </c>
-      <c r="AA17" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>s
 r
@@ -3044,31 +3747,31 @@
 p</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>z</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>z</t>
         </is>
       </c>
-      <c r="AD17" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>m
 n
 o</t>
         </is>
       </c>
-      <c r="AE17" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>o
 n
 m</t>
         </is>
       </c>
-      <c r="AG17" t="inlineStr">
+      <c r="AG9" t="inlineStr">
         <is>
           <t>import sys
 lines = sys.stdin.read().splitlines()
@@ -3077,13 +3780,505 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Python - Path Extension</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Path Extension. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Path
+### Output Format
+```
+txt
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>file-handling</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>file-paths</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>a.txt</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>txt</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>data.csv</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>csv</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>README</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>archive.tar.gz</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>gz</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>/tmp/x.py</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>py</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>no.dot</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>dot</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>image.PNG</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>PNG</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>name=input(); print(name.split(".")[-1] if "." in name else "none")</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Python - CSV Column Count</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for CSV Column Count. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: CSV row
+### Output Format
+```
+3
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>file-handling</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>csv-processing</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>a,b,c</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>one</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>x,y,z,w</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>blank</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>name,age,city</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>a,,b</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>row=input(); print(0 if row=="" else len(row.split(",")))</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AH11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>explanation</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>difficulty</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>bloomTaxonomy</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>subjects</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>topics</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>subTopics</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>companies</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>codingType</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>supportAllLanguages</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>enablePartialScore</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ignoreCase</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>testcase1_input</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>testcase1_output</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>testcase2_input</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>testcase2_output</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>testcase3_input</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>testcase3_output</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>testcase4_input</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>testcase4_output</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>testcase5_input</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>testcase5_output</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>testcase6_input</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>testcase6_output</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>testcase7_input</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>testcase7_output</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>preloadCode_python</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>solution_python</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>hints</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Python - Filter CSV Rows</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>A CSV file has a header 'name,score'. Use csv.DictReader to print the names of everyone scoring 40 or more, one per line.
 ### Input Format
@@ -3094,59 +4289,71 @@
 asha
 meera
 ```
+### Example Walkthrough
+In the sample, the rows are `asha,80`, `kabir,30`, and `meera,50`. Only `asha` and `meera` score `40` or more, so the program prints `asha` then `meera`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D2" t="n">
         <v>5</v>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>file-handling</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>csv</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>csv-processing</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O18" t="b">
+      <c r="O2" t="b">
         <v>0</v>
       </c>
-      <c r="P18" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q18" t="b">
-        <v>1</v>
-      </c>
-      <c r="R18" t="inlineStr">
+      <c r="P2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="b">
+        <v>1</v>
+      </c>
+      <c r="R2" t="inlineStr">
         <is>
           <t>name,score
 asha,80
@@ -3154,48 +4361,48 @@
 meera,55</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>asha
 meera</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>name,score
 sam,40</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>sam</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>name,score
 a,90
 b,20</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>name,score
 x,39</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>name,score
 y,0</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>name,score
 a,40
@@ -3203,19 +4410,19 @@
 c,40</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>a
 b
 c</t>
         </is>
       </c>
-      <c r="AD18" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>name,score</t>
         </is>
       </c>
-      <c r="AG18" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>import csv, sys
 for row in csv.DictReader(sys.stdin):
@@ -3224,13 +4431,13 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Python - Match by Extension</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Read N file names, then an extension (without the dot). Print the file names that end with that extension, in order, one per line.
 ### Input Format
@@ -3242,59 +4449,71 @@
 a.txt
 c.txt
 ```
+### Example Walkthrough
+In the sample, the file names are `a.txt`, `b.md`, and `c.txt`, and the extension to match is `txt`. Only `a.txt` and `c.txt` end with `.txt`, so the program prints them in order.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D3" t="n">
         <v>5</v>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>file-handling</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>text-processing</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>file-paths</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O19" t="b">
+      <c r="O3" t="b">
         <v>0</v>
       </c>
-      <c r="P19" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q19" t="b">
-        <v>1</v>
-      </c>
-      <c r="R19" t="inlineStr">
+      <c r="P3" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="b">
+        <v>1</v>
+      </c>
+      <c r="R3" t="inlineStr">
         <is>
           <t>3
 a.txt
@@ -3303,13 +4522,13 @@
 txt</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>a.txt
 c.txt</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>2
 x.md
@@ -3317,13 +4536,13 @@
 md</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>x.md
 y.md</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>2
 p.jpg
@@ -3331,30 +4550,30 @@
 jpg</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>p.jpg</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>0
 txt</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>1
 file.txt
 txt</t>
         </is>
       </c>
-      <c r="AA19" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>file.txt</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>3
 a.txt
@@ -3363,7 +4582,7 @@
 py</t>
         </is>
       </c>
-      <c r="AD19" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>4
 a.py
@@ -3373,13 +4592,13 @@
 py</t>
         </is>
       </c>
-      <c r="AE19" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>a.py
 c.py</t>
         </is>
       </c>
-      <c r="AG19" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>n = int(input())
 names = [input() for _ in range(n)]
@@ -3390,13 +4609,13 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Python - Build a Path</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Read N path segments and join them into a single path using pathlib, printing the result with '/' separators.
 ### Input Format
@@ -3406,59 +4625,71 @@
 ```
 home/user/file.txt
 ```
+### Example Walkthrough
+In the sample, the segments are `home`, `user`, and `file.txt`. Joined together with `/`, they form `home/user/file.txt`, which the program prints.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D4" t="n">
         <v>5</v>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>file-handling</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>text-processing</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>file-paths</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O20" t="b">
+      <c r="O4" t="b">
         <v>0</v>
       </c>
-      <c r="P20" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q20" t="b">
-        <v>1</v>
-      </c>
-      <c r="R20" t="inlineStr">
+      <c r="P4" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="b">
+        <v>1</v>
+      </c>
+      <c r="R4" t="inlineStr">
         <is>
           <t>3
 home
@@ -3466,35 +4697,35 @@
 file.txt</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>home/user/file.txt</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>2
 docs
 a.pdf</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>docs/a.pdf</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>1
 readme</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>readme</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>4
 a
@@ -3503,35 +4734,35 @@
 d.txt</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>a/b/c/d.txt</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>1
 single</t>
         </is>
       </c>
-      <c r="AA20" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>single</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>2
 x
 y</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>x/y</t>
         </is>
       </c>
-      <c r="AD20" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>3
 p
@@ -3539,12 +4770,12 @@
 r</t>
         </is>
       </c>
-      <c r="AE20" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>p/q/r</t>
         </is>
       </c>
-      <c r="AG20" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>from pathlib import PurePosixPath
 n = int(input())
@@ -3553,13 +4784,13 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Python - Longest Line</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Read the lines of a file and print the longest line. If several lines tie for longest, print the one that appears first.
 ### Input Format
@@ -3568,127 +4799,139 @@
 ```
 bbb
 ```
+### Example Walkthrough
+In the sample, the lines are `a`, `bbb`, and `cc`. The longest is `bbb`, so the program prints `bbb`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D5" t="n">
         <v>5</v>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>file-handling</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>text-processing</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>file-operations</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O21" t="b">
+      <c r="O5" t="b">
         <v>0</v>
       </c>
-      <c r="P21" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q21" t="b">
-        <v>1</v>
-      </c>
-      <c r="R21" t="inlineStr">
+      <c r="P5" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="b">
+        <v>1</v>
+      </c>
+      <c r="R5" t="inlineStr">
         <is>
           <t>a
 bbb
 cc</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>bbb</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>hello</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>hello</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>one
 two
 three</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>three</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>aa
 bb
 cc</t>
         </is>
       </c>
-      <c r="AA21" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>aa</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>short
 reallylongline
 med</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>reallylongline</t>
         </is>
       </c>
-      <c r="AD21" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>z
 zz
@@ -3696,12 +4939,12 @@
 zz</t>
         </is>
       </c>
-      <c r="AE21" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>zzz</t>
         </is>
       </c>
-      <c r="AG21" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>import sys
 lines = sys.stdin.read().splitlines()
@@ -3713,13 +4956,13 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Python - Count a Word in a File</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>The first line is a word to search for. The remaining lines are the file contents. Print how many times the word appears across those lines.
 ### Input Format
@@ -3729,140 +4972,152 @@
 ```
 3
 ```
+### Example Walkthrough
+In the sample, the word to find is `cat`, and the remaining lines are `cat dog cat` and `cat bird`. The word `cat` appears `3` times in total, so the program prints `3`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="D6" t="n">
         <v>5</v>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>file-handling</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>text-processing</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>file-operations</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O22" t="b">
+      <c r="O6" t="b">
         <v>0</v>
       </c>
-      <c r="P22" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q22" t="b">
-        <v>1</v>
-      </c>
-      <c r="R22" t="inlineStr">
+      <c r="P6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="b">
+        <v>1</v>
+      </c>
+      <c r="R6" t="inlineStr">
         <is>
           <t>cat
 the cat sat
 cat and cat</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>x
 x y x
 z</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>hi
 hello
 world</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>missing
 a b c</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>cat
 catapult cat</t>
         </is>
       </c>
-      <c r="AA22" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>a
 a a a
 a a</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AD22" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>dog
 no match here</t>
         </is>
       </c>
-      <c r="AE22" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AG22" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>import sys
 lines = sys.stdin.read().splitlines()
@@ -3872,13 +5127,13 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Python - Unique Lines</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Read the lines of a file and print each distinct line once, keeping the order of first appearance.
 ### Input Format
@@ -3889,59 +5144,71 @@
 b
 c
 ```
+### Example Walkthrough
+In the sample, the lines are `a`, `a`, `b`, `c`, and `b`. Keeping only the first occurrence of each gives `a`, `b`, and `c`, in that order.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D7" t="n">
         <v>5</v>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>file-handling</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>text-processing</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>file-operations</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O23" t="b">
+      <c r="O7" t="b">
         <v>0</v>
       </c>
-      <c r="P23" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q23" t="b">
-        <v>1</v>
-      </c>
-      <c r="R23" t="inlineStr">
+      <c r="P7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="b">
+        <v>1</v>
+      </c>
+      <c r="R7" t="inlineStr">
         <is>
           <t>a
 b
@@ -3950,45 +5217,45 @@
 b</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>a
 b
 c</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>one
 one</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>one</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>a
 a
@@ -3996,12 +5263,12 @@
 a</t>
         </is>
       </c>
-      <c r="AA23" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>p
 q
@@ -4010,28 +5277,28 @@
 q</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>p
 q
 r</t>
         </is>
       </c>
-      <c r="AD23" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>z
 y
 x</t>
         </is>
       </c>
-      <c r="AE23" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>z
 y
 x</t>
         </is>
       </c>
-      <c r="AG23" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>import sys
 seen = []
@@ -4043,15 +5310,15 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Python - Student Report CSV</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>A CSV has header 'name,`m1`,`m2`,`m3`' and data rows. Print a new CSV with header 'name,total,average', where average is rounded to 1 decimal place, one row per student.
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>A CSV has header 'name,m1,m2,m3' and data rows. Print a new CSV with header 'name,total,average', where average is rounded to 1 decimal place, one row per student.
 ### Input Format
 - Line 1: Header 'name,`m1`,`m2`,`m3`'
 - Next lines: data rows
@@ -4061,145 +5328,157 @@
 asha,270,90.0
 kabir,180,60.0
 ```
+### Example Walkthrough
+In the sample, `asha` has marks `90, 90, 90` (total `270`, average `90.0`), and `kabir` has marks `60, 60, 60` (total `180`, average `60.0`), so the program prints the header followed by both rows.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="D8" t="n">
         <v>5</v>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>file-handling</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>csv</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>csv-processing</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O24" t="b">
+      <c r="O8" t="b">
         <v>0</v>
       </c>
-      <c r="P24" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q24" t="b">
-        <v>1</v>
-      </c>
-      <c r="R24" t="inlineStr">
+      <c r="P8" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="b">
+        <v>1</v>
+      </c>
+      <c r="R8" t="inlineStr">
         <is>
           <t>name,m1,m2,m3
 asha,80,90,100
 kabir,60,60,60</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>name,total,average
 asha,270,90.0
 kabir,180,60.0</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>name,m1,m2,m3
 sam,50,50,50</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>name,total,average
 sam,150,50.0</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>name,m1,m2,m3
 a,10,20,30</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>name,total,average
 a,60,20.0</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>name,m1,m2,m3
 zed,0,0,0</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>name,total,average
 zed,0,0.0</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>name,m1,m2,m3
 x,100,100,100</t>
         </is>
       </c>
-      <c r="AA24" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>name,total,average
 x,300,100.0</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>name,m1,m2,m3
 p,1,2,2
 q,3,3,3</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>name,total,average
 p,5,1.7
 q,9,3.0</t>
         </is>
       </c>
-      <c r="AD24" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>name,m1,m2,m3</t>
         </is>
       </c>
-      <c r="AE24" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>name,total,average</t>
         </is>
       </c>
-      <c r="AG24" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>import csv, sys
 reader = csv.DictReader(sys.stdin)
@@ -4213,13 +5492,690 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Python - JSON Key Value</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for JSON Key Value. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: JSON object
+- Line 2: Key
+### Output Format
+```
+Asha
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>file-handling</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>json-processing</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O9" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="b">
+        <v>1</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>{"name":"Asha","age":19}
+name</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Asha</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>{"x":5}
+y</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>{}
+a</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>{"city":"Pune"}
+city</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>{"a":1,"b":2}
+b</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>{"ok":true}
+ok</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>{"v":null}
+v</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>import json
+d=json.loads(input()); k=input(); print(d.get(k,"Missing"))</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Python - Glob Suffix Match</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Glob Suffix Match. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: File names
+- Line 2: Suffix
+### Output Format
+```
+2
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>file-handling</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>glob-pattern-matching</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>a.py b.txt c.py
+.py</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>one.csv two.csv
+.csv</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>README test.md
+.md</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>a b
+.py</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>x.JSON y.json
+.json</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>data1.txt data2.csv
+.txt</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>main.py
+.py</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>names=input().split(); suffix=input(); print(sum(1 for n in names if n.endswith(suffix)))</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Python - Context Summary</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Context Summary. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: N
+- Next N lines: Text
+### Output Format
+```
+4
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>python - Set 3</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>file-handling</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>context-managed-files</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>2
+ab
+cd</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1
+hello</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>3
+a
+bb
+ccc</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>2
+abc</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+ </t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>4
+x
+y
+z
+w</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>n=int(input()); total=0
+for _ in range(n): total+=len(input())
+print(total)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AH11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>explanation</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>difficulty</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>bloomTaxonomy</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>subjects</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>topics</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>subTopics</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>companies</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>codingType</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>supportAllLanguages</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>enablePartialScore</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ignoreCase</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>testcase1_input</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>testcase1_output</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>testcase2_input</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>testcase2_output</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>testcase3_input</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>testcase3_output</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>testcase4_input</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>testcase4_output</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>testcase5_input</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>testcase5_output</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>testcase6_input</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>testcase6_output</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>testcase7_input</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>testcase7_output</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>preloadCode_python</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>solution_python</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>hints</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Python - Sum JSON Values</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Read one line of JSON describing an object that maps names to numbers, and print the total of all the values.
 ### Input Format
@@ -4228,129 +6184,141 @@
 ```
 60
 ```
+### Example Walkthrough
+In the sample, the JSON object is `{"a": 20, "b": 40}`. Adding its values gives `20 + 40 = 60`, so the program prints `60`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="D2" t="n">
         <v>5</v>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>file-handling</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>json</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>json-processing</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O25" t="b">
+      <c r="O2" t="b">
         <v>0</v>
       </c>
-      <c r="P25" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q25" t="b">
-        <v>1</v>
-      </c>
-      <c r="R25" t="inlineStr">
+      <c r="P2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="b">
+        <v>1</v>
+      </c>
+      <c r="R2" t="inlineStr">
         <is>
           <t>{"a": 10, "b": 20, "c": 30}</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>{"x": 5}</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>{"p": 1, "q": 2}</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>{"neg": -10, "pos": 10}</t>
         </is>
       </c>
-      <c r="AA25" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>{"z": 0}</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AD25" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>{"m": 100, "n": 200, "o": 300}</t>
         </is>
       </c>
-      <c r="AE25" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>600</t>
         </is>
       </c>
-      <c r="AG25" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>import json
 data = json.loads(input())
@@ -4358,13 +6326,13 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Python - Most Common Word in File</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Read all the lines of a file and print the word that appears most often across the whole file. If several tie, print the one that appears first.
 ### Input Format
@@ -4373,131 +6341,143 @@
 ```
 the
 ```
+### Example Walkthrough
+In the sample, the line is `the cat the dog the bird`. The word `the` appears `3` times, more than any other word, so the program prints `the`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D3" t="n">
         <v>5</v>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>file-handling</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>text-processing</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>file-operations</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O26" t="b">
+      <c r="O3" t="b">
         <v>0</v>
       </c>
-      <c r="P26" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q26" t="b">
-        <v>1</v>
-      </c>
-      <c r="R26" t="inlineStr">
+      <c r="P3" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="b">
+        <v>1</v>
+      </c>
+      <c r="R3" t="inlineStr">
         <is>
           <t>the cat
 the dog
 the</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>the</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>hello world</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>hello</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>a b a</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>solo</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>solo</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>x y x y</t>
         </is>
       </c>
-      <c r="AA26" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>one two three</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>one</t>
         </is>
       </c>
-      <c r="AD26" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>cat dog cat bird cat</t>
         </is>
       </c>
-      <c r="AE26" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>cat</t>
         </is>
       </c>
-      <c r="AG26" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>import sys
 words = sys.stdin.read().split()
@@ -4512,13 +6492,13 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Python - Group CSV by Category</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>A CSV has header 'category,amount'. Print each category's total as 'category:total', with categories sorted alphabetically.
 ### Input Format
@@ -4529,59 +6509,71 @@
 food:130
 travel:50
 ```
+### Example Walkthrough
+In the sample, the rows are `food,100`, `travel,50`, and `food,30`. The `food` entries total `130` and `travel` totals `50`, so the program prints `food:130` then `travel:50`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="D4" t="n">
         <v>5</v>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>file-handling</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>csv</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>csv-processing</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O27" t="b">
+      <c r="O4" t="b">
         <v>0</v>
       </c>
-      <c r="P27" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q27" t="b">
-        <v>1</v>
-      </c>
-      <c r="R27" t="inlineStr">
+      <c r="P4" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="b">
+        <v>1</v>
+      </c>
+      <c r="R4" t="inlineStr">
         <is>
           <t>category,amount
 food,100
@@ -4589,64 +6581,64 @@
 food,30</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>food:130
 travel:50</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>category,amount
 rent,500</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>rent:500</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>category,amount
 a,5
 a,5</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>a:10</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>category,amount</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>category,amount
 x,0</t>
         </is>
       </c>
-      <c r="AA27" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>x:0</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>category,amount
 c,-10
 c,20</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>c:10</t>
         </is>
       </c>
-      <c r="AD27" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>category,amount
 z,1
@@ -4654,14 +6646,14 @@
 x,3</t>
         </is>
       </c>
-      <c r="AE27" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>x:3
 y:2
 z:1</t>
         </is>
       </c>
-      <c r="AG27" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>import csv, sys
 totals = {}
@@ -4673,13 +6665,13 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Python - Average per Name</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>A CSV has header 'name,score' with possibly several rows per name. Print each name's average score (rounded to 1 decimal place) as 'name:average', with names sorted alphabetically.
 ### Input Format
@@ -4690,59 +6682,71 @@
 asha:90.0
 kabir:60.0
 ```
+### Example Walkthrough
+In the sample, the rows are `asha,90` and `kabir,60`. Each name has a single score, so their averages are `90.0` and `60.0`, printed as `asha:90.0` then `kabir:60.0`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="D5" t="n">
         <v>5</v>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>file-handling</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>csv</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>csv-processing</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O28" t="b">
+      <c r="O5" t="b">
         <v>0</v>
       </c>
-      <c r="P28" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q28" t="b">
-        <v>1</v>
-      </c>
-      <c r="R28" t="inlineStr">
+      <c r="P5" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="b">
+        <v>1</v>
+      </c>
+      <c r="R5" t="inlineStr">
         <is>
           <t>name,score
 asha,80
@@ -4750,24 +6754,24 @@
 kabir,60</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>asha:90.0
 kabir:60.0</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>name,score
 sam,70</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>sam:70.0</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>name,score
 a,10
@@ -4775,24 +6779,24 @@
 a,30</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>a:20.0
 b:20.0</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>name,score
 x,0</t>
         </is>
       </c>
-      <c r="Y28" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>x:0.0</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>name,score
 z,1
@@ -4800,12 +6804,12 @@
 z,3</t>
         </is>
       </c>
-      <c r="AA28" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>z:2.0</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>name,score
 a,100
@@ -4813,19 +6817,19 @@
 c,75</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>a:100.0
 b:50.0
 c:75.0</t>
         </is>
       </c>
-      <c r="AD28" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>name,score</t>
         </is>
       </c>
-      <c r="AG28" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>import csv, sys
 scores = {}
@@ -4837,13 +6841,13 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Python - Match Multiple Extensions</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Read N file names, then a line of allowed extensions separated by spaces (no dots). Print the file names whose extension is in the allowed list, in their original order.
 ### Input Format
@@ -4856,59 +6860,71 @@
 c.md
 d.txt
 ```
+### Example Walkthrough
+In the sample, the file names are `a.txt`, `b.py`, `c.md`, and `d.txt`, and the allowed extensions are `txt` and `md`. All but `b.py` match, so the program prints `a.txt`, `c.md`, and `d.txt` in their original order.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D6" t="n">
         <v>5</v>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>file-handling</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>text-processing</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>file-paths</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O29" t="b">
+      <c r="O6" t="b">
         <v>0</v>
       </c>
-      <c r="P29" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q29" t="b">
-        <v>1</v>
-      </c>
-      <c r="R29" t="inlineStr">
+      <c r="P6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="b">
+        <v>1</v>
+      </c>
+      <c r="R6" t="inlineStr">
         <is>
           <t>4
 a.txt
@@ -4918,14 +6934,14 @@
 txt md</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>a.txt
 c.md
 d.txt</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>2
 x.jpg
@@ -4933,12 +6949,12 @@
 png</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>y.png</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>3
 p.doc
@@ -4947,32 +6963,32 @@
 doc pdf</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>p.doc
 q.pdf
 r.doc</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>0
 txt</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>1
 file.txt
 txt</t>
         </is>
       </c>
-      <c r="AA29" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>file.txt</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>3
 a.txt
@@ -4981,7 +6997,7 @@
 py</t>
         </is>
       </c>
-      <c r="AD29" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>2
 a.tar.gz
@@ -4989,13 +7005,13 @@
 gz zip</t>
         </is>
       </c>
-      <c r="AE29" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>a.tar.gz
 b.zip</t>
         </is>
       </c>
-      <c r="AG29" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>from pathlib import PurePosixPath
 n = int(input())
@@ -5007,13 +7023,13 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Python - Word Frequency as JSON</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Read a sentence and print a JSON object mapping each word to how many times it appears, with the keys sorted alphabetically. Use json.dumps with `sort_keys`.
 ### Input Format
@@ -5022,129 +7038,141 @@
 ```
 {"a": 2, "b": 1, "c": 1}
 ```
+### Example Walkthrough
+In the sample, the sentence is `a b a c`. The word `a` appears `2` times and `b` and `c` appear once each, so the program prints `{"a": 2, "b": 1, "c": 1}` with keys sorted alphabetically.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="D7" t="n">
         <v>5</v>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>file-handling</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>json</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>json-processing</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O30" t="b">
+      <c r="O7" t="b">
         <v>0</v>
       </c>
-      <c r="P30" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q30" t="b">
-        <v>1</v>
-      </c>
-      <c r="R30" t="inlineStr">
+      <c r="P7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="b">
+        <v>1</v>
+      </c>
+      <c r="R7" t="inlineStr">
         <is>
           <t>a b a c</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>{"a": 2, "b": 1, "c": 1}</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>hello hello world</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>{"hello": 2, "world": 1}</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>x y z</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>{"x": 1, "y": 1, "z": 1}</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>single</t>
         </is>
       </c>
-      <c r="Y30" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>{"single": 1}</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>a a a a</t>
         </is>
       </c>
-      <c r="AA30" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>{"a": 4}</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>z y x w v</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>{"v": 1, "w": 1, "x": 1, "y": 1, "z": 1}</t>
         </is>
       </c>
-      <c r="AD30" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>cat dog cat bird</t>
         </is>
       </c>
-      <c r="AE30" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>{"bird": 1, "cat": 2, "dog": 1}</t>
         </is>
       </c>
-      <c r="AG30" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>import json
 words = input().split()
@@ -5155,13 +7183,13 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Python - Validate Records</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Read N records, each 'name,age'. A record is valid only if the age is a whole number greater than 0. Print 'valid X invalid Y' with the counts of valid and invalid records.
 ### Input Format
@@ -5171,59 +7199,71 @@
 ```
 valid 1 invalid 2
 ```
+### Example Walkthrough
+In the sample, the records are `asha,20` (a valid positive age), `kabir,-5` (an invalid non-positive age), and `meera,abc` (an invalid, non-numeric age). That gives `1` valid and `2` invalid records, so the program prints `valid 1 invalid 2`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
 - Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="D8" t="n">
         <v>5</v>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>python-fundamentals</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>analyze</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>file-handling</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>text-processing</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>file-operations</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O31" t="b">
+      <c r="O8" t="b">
         <v>0</v>
       </c>
-      <c r="P31" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q31" t="b">
-        <v>1</v>
-      </c>
-      <c r="R31" t="inlineStr">
+      <c r="P8" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="b">
+        <v>1</v>
+      </c>
+      <c r="R8" t="inlineStr">
         <is>
           <t>3
 asha,20
@@ -5231,57 +7271,57 @@
 sam,abc</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>valid 1 invalid 2</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>2
 a,10
 b,30</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>valid 2 invalid 0</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>2
 x,0
 y,5</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>valid 1 invalid 1</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>valid 0 invalid 0</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>1
 zed,1</t>
         </is>
       </c>
-      <c r="AA31" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>valid 1 invalid 0</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>4
 a,1
@@ -5290,23 +7330,23 @@
 d,2</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>valid 2 invalid 2</t>
         </is>
       </c>
-      <c r="AD31" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>1
 p,0</t>
         </is>
       </c>
-      <c r="AE31" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>valid 0 invalid 1</t>
         </is>
       </c>
-      <c r="AG31" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>n = int(input())
 valid = invalid = 0
@@ -5323,6 +7363,490 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Python - CSV Sum Column</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for CSV Sum Column. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: N
+- Next N lines: name,value
+### Output Format
+```
+30
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>file-handling</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>csv-processing</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O9" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="b">
+        <v>1</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>2
+a,10
+b,20</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>1
+x,5</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>3
+a,1
+b,2
+c,3</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>2
+a,-1
+b,1</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>1
+item,0</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>4
+a,10
+b,0
+c,-5
+d,1</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>n=int(input()); total=0
+for _ in range(n): total+=int(input().split(",")[1])
+print(total)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Python - JSON List Average</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for JSON List Average. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: JSON list
+### Output Format
+```
+2.0
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>file-handling</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>json-processing</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>[1,2,3]</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>[5]</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>[0,10]</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>[-1,1]</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>[10,20,30,40]</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>[100,-100,50]</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>16.666666666666668</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>import json
+nums=json.loads(input()); print(sum(nums)/len(nums))</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Python - Missing File Guard</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A supplemental Python practice task for Missing File Guard. Read the input values and print the required result exactly.
+### Input Format
+- Line 1: Available names
+- Line 2: Requested name
+### Output Format
+```
+Found
+```
+### Constraints
+- Inputs follow the described format.
+- Print exactly the requested output with no extra text.</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>python - Set 4</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>file-handling</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>file-errors</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>a.txt b.txt
+a.txt</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Found</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>data.csv
+missing.csv</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>none
+a.txt</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>one two
+two</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Found</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>README
+README</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Found</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>x y z
+a</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>report.pdf notes.doc
+notes.doc</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>Found</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>available=set(input().split()); name=input(); print("Found" if name in available else "Missing")</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/content/Question Bank/Coding Questions/Unit 11 - File Handling/Unit 11 - File Handling - Coding Questions.xlsx
+++ b/content/Question Bank/Coding Questions/Unit 11 - File Handling/Unit 11 - File Handling - Coding Questions.xlsx
@@ -1904,17 +1904,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Line Counter. Read the input values and print the required result exactly.
+          <t>A batch import tool is told upfront how many rows a data file contains, then reads through every row one by one to make sure none are missing, and finally confirms the total number of rows it processed.
+Write a program that reads a whole number N, then reads N more lines (treat them as the file's contents, one row per line), and prints N once all the lines have been read.
 ### Input Format
-- Line 1: N
-- Next N lines: Text
+- Line 1: N, the number of lines in the file
+- Next N lines: the file's contents
 ### Output Format
 ```
 3
 ```
+### Example Walkthrough
+In the sample, N is 3 and the file contains the lines `a`, `b`, and `c`. After reading all three lines, the program prints the total, `3`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- N is a valid whole number matching the number of lines that follow.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -2076,17 +2079,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Longest File Line. Read the input values and print the required result exactly.
+          <t>A log-file linter checks the length of every line in a file to catch the single longest one, since lines over a certain length must be flagged for readability.
+Write a program that reads a whole number N, then reads N more lines (treat them as the file's contents), and prints the length of the longest line. If N is 0, print `0`.
 ### Input Format
-- Line 1: N
-- Next N lines: Text
+- Line 1: N, the number of lines in the file
+- Next N lines: the file's contents
 ### Output Format
 ```
 3
 ```
+### Example Walkthrough
+In the sample, N is 3 and the lines are `a` (length 1), `abc` (length 3), and `ab` (length 2). The longest is `abc` with length 3, so the program prints `3`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- N is a valid whole number matching the number of lines that follow.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -3788,16 +3794,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Path Extension. Read the input values and print the required result exactly.
+          <t>A media library organizes uploaded files by type using the text after the last dot in the file name, but some files are uploaded with no dot at all and need special handling.
+Write a program that reads a file name and prints the text after the last `.` in the name (without the dot itself). If the name has no dot, print `none`.
 ### Input Format
-- Line 1: Path
+- Line 1: A file name
 ### Output Format
 ```
 txt
 ```
+### Example Walkthrough
+In the sample, the file name is `a.txt`. The text after the last dot is `txt`, so the program prints `txt`. A name with no dot, like `README`, would print `none`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- The input is a valid file name with no spaces.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -3941,16 +3950,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for CSV Column Count. Read the input values and print the required result exactly.
+          <t>A CSV import validator checks how many columns each row of a spreadsheet export has, to make sure every row matches the expected column count before the data is processed further.
+Write a program that reads one line representing a CSV row (values separated by commas) and prints how many columns it has. If the line is empty, print `0`.
 ### Input Format
-- Line 1: CSV row
+- Line 1: A CSV row (comma-separated values)
 ### Output Format
 ```
 3
 ```
+### Example Walkthrough
+In the sample, the row is `a,b,c`. Splitting on commas gives three values, so the program prints `3`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- The input is a single valid line representing one CSV row.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -5500,17 +5512,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for JSON Key Value. Read the input values and print the required result exactly.
+          <t>A config loader reads a single JSON object representing an app's settings and needs to fetch one setting by name, reporting `Missing` if that setting isn't present in the file.
+Write a program that reads a line of JSON representing an object, parses it, reads a key on the next line, and prints the value for that key if it exists, or `Missing` otherwise.
 ### Input Format
-- Line 1: JSON object
-- Line 2: Key
+- Line 1: A JSON object
+- Line 2: The key to look up
 ### Output Format
 ```
 Asha
 ```
+### Example Walkthrough
+In the sample, the JSON is `{"name":"Asha","age":19}` and the key is `name`. Looking up `name` in the parsed object gives `Asha`, so the program prints `Asha`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- The input is valid JSON representing an object.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -5662,17 +5677,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Glob Suffix Match. Read the input values and print the required result exactly.
+          <t>A backup tool scans a folder's file list to count how many files match a certain extension pattern (like a simplified `*.py` glob), to decide whether a backup step is needed for that file type.
+Write a program that reads a line of space-separated file names, reads a suffix on the next line, and prints how many of the file names end with that exact suffix.
 ### Input Format
-- Line 1: File names
-- Line 2: Suffix
+- Line 1: Space-separated file names
+- Line 2: A suffix (e.g. `.py`)
 ### Output Format
 ```
 2
 ```
+### Example Walkthrough
+In the sample, the file names are `a.py b.txt c.py` and the suffix is `.py`. Two of the three file names (`a.py` and `c.py`) end with `.py`, so the program prints `2`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- The inputs are valid, non-empty lines of text.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -5823,17 +5841,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Context Summary. Read the input values and print the required result exactly.
+          <t>A document analytics tool reads through a file's contents (opened safely with a `with` statement so it always closes properly) and needs to report the total number of characters across all its lines, not counting the line breaks between them.
+Write a program that reads a whole number N, then reads N more lines (treat them as the file's contents), and prints the total number of characters across all N lines combined. If N is 0, print `0`.
 ### Input Format
-- Line 1: N
-- Next N lines: Text
+- Line 1: N, the number of lines in the file
+- Next N lines: the file's contents
 ### Output Format
 ```
 4
 ```
+### Example Walkthrough
+In the sample, N is 2 and the lines are `ab` (2 characters) and `cd` (2 characters). Adding their lengths gives 2 + 2 = 4, so the program prints `4`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- N is a valid whole number matching the number of lines that follow.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -7371,17 +7392,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for CSV Sum Column. Read the input values and print the required result exactly.
+          <t>An accounting import tool reads N rows of a CSV export where each row has an item label and an amount separated by a comma, and needs the total of just the amount column across all rows.
+Write a program that reads a whole number N, then reads N more lines each in the form `label,amount`, and prints the sum of the amount values. If N is 0, print `0`.
 ### Input Format
-- Line 1: N
-- Next N lines: name,value
+- Line 1: N, the number of rows
+- Next N lines: `label,amount`
 ### Output Format
 ```
 30
 ```
+### Example Walkthrough
+In the sample, N is 2 with rows `a,10` and `b,20`. Adding the amounts gives 10 + 20 = 30, so the program prints `30`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- N is a valid whole number, and every amount is a valid whole number.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -7540,16 +7564,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for JSON List Average. Read the input values and print the required result exactly.
+          <t>A fitness app stores a week's daily step counts as a JSON array in a log file and needs the average steps per day to show on the weekly summary screen.
+Write a program that reads a line containing a JSON array of numbers, parses it, and prints the average of the numbers (their sum divided by how many there are).
 ### Input Format
-- Line 1: JSON list
+- Line 1: A JSON array of numbers
 ### Output Format
 ```
 2.0
 ```
+### Example Walkthrough
+In the sample, the array is `[1,2,3]`. The average is (1 + 2 + 3) / 3 = 2.0, so the program prints `2.0`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- The input is a valid, non-empty JSON array of numbers.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -7694,17 +7721,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A supplemental Python practice task for Missing File Guard. Read the input values and print the required result exactly.
+          <t>A file cleanup script checks a requested file name against the set of files that actually exist in a folder before attempting to open or delete it, to avoid a crash from trying to act on a file that isn't there.
+Write a program that reads a line of space-separated file names (the files that exist), reads one more file name on the next line, and prints `Found` if that file name is in the list, or `Missing` otherwise.
 ### Input Format
-- Line 1: Available names
-- Line 2: Requested name
+- Line 1: Space-separated file names (the files that exist)
+- Line 2: The file name being requested
 ### Output Format
 ```
 Found
 ```
+### Example Walkthrough
+In the sample, the existing files are `a.txt b.txt` and the requested file is `a.txt`. Since `a.txt` is in the list, the program prints `Found`.
 ### Constraints
-- Inputs follow the described format.
-- Print exactly the requested output with no extra text.</t>
+- The inputs are valid, non-empty lines of text.
+- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D11" t="n">

--- a/content/Question Bank/Coding Questions/Unit 11 - File Handling/Unit 11 - File Handling - Coding Questions.xlsx
+++ b/content/Question Bank/Coding Questions/Unit 11 - File Handling/Unit 11 - File Handling - Coding Questions.xlsx
@@ -7,10 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set 4" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - Coding - Unit 11" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH11"/>
+  <dimension ref="A1:AH41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -599,19 +596,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-Riya is the secretary of her hostel's cultural committee, and the warden hands her a plain text file of announcements — one announcement per line. Before printing notices, she wants a quick check of how many announcements the file holds. Write a program that reads all the lines given as input (treat them as the file's contents) and prints the number of lines.
-### Input Format
-- All lines: the file contents (each line is one announcement)
-### Output Format
-```
-3
-```
+          <t>Riya is the secretary of her hostel's cultural committee, and the warden hands her a plain text file of announcements — one announcement per line. Before printing notices, she wants a quick check of how many announcements the file holds. Write a program that reads all the lines given as input (treat them as the file's contents) and prints the number of lines.
 ### Example Walkthrough
 The sample input has three lines: `a`, `b`, and `c`. Reading them one by one, the count goes 1, 2, 3. Since there are 3 lines in total, the program prints `3`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -747,7 +737,7 @@
       <c r="AG2" t="inlineStr">
         <is>
           <t>import sys
-lines = sys.stdin.read().splitlines()
+lines = sys.stdin.read().splitlines()   # each input line stands in for one line of a file
 print(len(lines))</t>
         </is>
       </c>
@@ -760,19 +750,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-The canteen at Arjun's college exports its daily sales as CSV (comma-separated values), where each row is a list of entries separated by commas. Before processing a row, Arjun wants to know how many entries it contains. Write a program that reads one CSV row using Python's csv module and prints how many fields (comma-separated pieces) it has.
-### Input Format
-- Line 1: A CSV row
-### Output Format
-```
-3
-```
+          <t>The canteen at Arjun's college exports its daily sales as CSV (comma-separated values), where each row is a list of entries separated by commas. Before processing a row, Arjun wants to know how many entries it contains. Write a program that reads one CSV row using Python's csv module and prints how many fields (comma-separated pieces) it has.
 ### Example Walkthrough
 The sample row is `a,b,c`. Splitting it at the commas gives three fields — `a`, `b`, and `c` — so the program prints `3`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -905,7 +888,7 @@
       <c r="AG3" t="inlineStr">
         <is>
           <t>import csv, sys
-row = next(csv.reader(sys.stdin))
+row = next(csv.reader(sys.stdin))   # parse stdin as if reading one CSV row from a file
 print(len(row))</t>
         </is>
       </c>
@@ -918,19 +901,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-The college fest website stores each participant's details as JSON, a text format made of `"key": value` pairs inside curly braces. Meera at the registration desk only needs each participant's name. Write a program that reads one line of JSON describing a person and prints the value stored under its 'name' field.
-### Input Format
-- Line 1: A JSON object
-### Output Format
-```
-Asha
-```
+          <t>The college fest website stores each participant's details as JSON, a text format made of `"key": value` pairs inside curly braces. Meera at the registration desk only needs each participant's name. Write a program that reads one line of JSON describing a person and prints the value stored under its 'name' field.
 ### Example Walkthrough
 The sample input is `{"name": "Asha", "age": 20}`. Loading it with `json.loads` gives a dictionary, and looking up the `name` key returns `Asha`, which is printed.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -1058,7 +1034,7 @@
       <c r="AG4" t="inlineStr">
         <is>
           <t>import json
-data = json.loads(input())
+data = json.loads(input())   # parse text the same way json.load() would read from an open file
 print(data["name"])</t>
         </is>
       </c>
@@ -1071,19 +1047,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-The librarian is digitising old question papers, and files arrive with all kinds of names — some end in .txt, some in .pdf, some in .docx. To sort them into folders she first needs each file's extension. Write a program that reads a file name and, using Python's pathlib module, prints its extension including the leading dot (for example '.txt').
-### Input Format
-- Line 1: A file name
-### Output Format
-```
-.txt
-```
+          <t>The librarian is digitising old question papers, and files arrive with all kinds of names — some end in .txt, some in .pdf, some in .docx. To sort them into folders she first needs each file's extension. Write a program that reads a file name and, using Python's pathlib module, prints its extension including the leading dot (for example '.txt').
 ### Example Walkthrough
 For the sample name `file.txt`, pathlib's `Path('file.txt').suffix` looks at everything from the last dot onwards, which is `.txt`, so that is exactly what gets printed.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -1206,7 +1175,7 @@
       <c r="AG5" t="inlineStr">
         <is>
           <t>from pathlib import PurePosixPath
-print(PurePosixPath(input()).suffix)</t>
+print(PurePosixPath(input()).suffix)   # pathlib pulls out the extension, dot included</t>
         </is>
       </c>
     </row>
@@ -1218,20 +1187,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-Coach Nair records his cricket team's practice scores in a CSV file: a header row 'name,score' followed by one row per player. At the end of the session he wants the team's total. Write a program that reads the CSV using csv.DictReader and prints the total of the 'score' column.
-### Input Format
-- Line 1: Header 'name,score'
-- Next lines: data rows
-### Output Format
-```
-170
-```
+          <t>Coach Nair records his cricket team's practice scores in a CSV file: a header row 'name,score' followed by one row per player. At the end of the session he wants the team's total. Write a program that reads the CSV using csv.DictReader and prints the total of the 'score' column.
 ### Example Walkthrough
 The sample data rows are `asha,80` and `kabir,90`. DictReader turns each row into a dictionary using the header names as keys, so the program adds the score values 80 + 90 = 170 and prints `170`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1377,7 +1338,7 @@
         <is>
           <t>import csv, sys
 total = 0
-for row in csv.DictReader(sys.stdin):
+for row in csv.DictReader(sys.stdin):   # DictReader reads stdin as CSV rows keyed by the header
     total += int(row["score"])
 print(total)</t>
         </is>
@@ -1391,19 +1352,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-Dev's mobile recharge app logs how much data he used each day as a JSON list of numbers, like `[1, 2, 3]`. He wants his total usage for the period in one shot. Write a program that reads one line containing a JSON list of numbers and prints their sum.
-### Input Format
-- Line 1: A JSON list of numbers
-### Output Format
-```
-10
-```
+          <t>Dev's mobile recharge app logs how much data he used each day as a JSON list of numbers, like `[1, 2, 3]`. He wants his total usage for the period in one shot. Write a program that reads one line containing a JSON list of numbers and prints their sum.
 ### Example Walkthrough
 The sample input `[1, 2, 3, 4]` becomes a normal Python list after `json.loads`. Adding the values gives 1 + 2 + 3 + 4 = 10, so the program prints `10`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1536,7 +1490,7 @@
       <c r="AG7" t="inlineStr">
         <is>
           <t>import json
-numbers = json.loads(input())
+numbers = json.loads(input())   # parse a JSON array the same way json.load() would from a file
 print(sum(numbers))</t>
         </is>
       </c>
@@ -1549,21 +1503,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-The coding club is setting up its website, and all the settings live in a config file with lines like 'key=value' (for example 'port=8080'). Tanvi needs a quick way to look up any one setting. Write a program that reads N, then N 'key=value' lines, then a key to look up. Print the value stored for that key, or 'Not Found' if the key does not appear in the file.
-### Input Format
-- Line 1: N
-- Next N lines: 'key=value'
-- Last line: a key
-### Output Format
-```
-8080
-```
+          <t>The coding club is setting up its website, and all the settings live in a config file with lines like 'key=value' (for example 'port=8080'). Tanvi needs a quick way to look up any one setting. Write a program that reads N, then N 'key=value' lines, then a key to look up. Print the value stored for that key, or 'Not Found' if the key does not appear in the file.
 ### Example Walkthrough
 N is 2, and the lines `host=localhost` and `port=8080` are each split at the '=' into a key and a value. The key to look up is `port`, which matches the second line, so the program prints `8080`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1716,9 +1661,9 @@
           <t>n = int(input())
 config = {}
 for _ in range(n):
-    key, value = input().split("=")
+    key, value = input().split("=")   # simulate reading key=value lines from a config file
     config[key] = value
-print(config.get(input(), "Not Found"))</t>
+print(config.get(input(), "Not Found"))   # look up a key, fall back if it is missing</t>
         </is>
       </c>
     </row>
@@ -1730,21 +1675,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-For sports day, volunteers noted each participant on paper as a name and an age separated by a space. The events team now needs the same list as a CSV file to upload to the college portal. Write a program that reads N records of 'name age' and writes each one out as a CSV row 'name,age' using the csv module.
-### Input Format
-- Line 1: N
-- Next N lines: 'name age'
-### Output Format
-```
-asha,20
-kabir,21
-```
+          <t>For sports day, volunteers noted each participant on paper as a name and an age separated by a space. The events team now needs the same list as a CSV file to upload to the college portal. Write a program that reads N records of 'name age' and writes each one out as a CSV row 'name,age' using the csv module.
 ### Example Walkthrough
 N is 2, so the program reads `asha 20` and `kabir 21`, splits each record at the space, and writes the two parts joined by a comma instead: first `asha,20`, then `kabir,21`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1888,7 +1824,7 @@
       <c r="AG9" t="inlineStr">
         <is>
           <t>import csv, sys
-writer = csv.writer(sys.stdout)
+writer = csv.writer(sys.stdout)   # write rows to stdout the way csv.writer writes to an open file
 n = int(input())
 for _ in range(n):
     name, age = input().split()
@@ -1906,18 +1842,11 @@
         <is>
           <t>A batch import tool is told upfront how many rows a data file contains, then reads through every row one by one to make sure none are missing, and finally confirms the total number of rows it processed.
 Write a program that reads a whole number N, then reads N more lines (treat them as the file's contents, one row per line), and prints N once all the lines have been read.
-### Input Format
-- Line 1: N, the number of lines in the file
-- Next N lines: the file's contents
-### Output Format
-```
-3
-```
 ### Example Walkthrough
 In the sample, N is 3 and the file contains the lines `a`, `b`, and `c`. After reading all three lines, the program prints the total, `3`.
 ### Constraints
 - N is a valid whole number matching the number of lines that follow.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -2066,7 +1995,7 @@
       <c r="AG10" t="inlineStr">
         <is>
           <t>n=int(input())
-for _ in range(n): input()
+for _ in range(n): input()   # read and discard each line, like scanning past a file's rows
 print(n)</t>
         </is>
       </c>
@@ -2081,18 +2010,11 @@
         <is>
           <t>A log-file linter checks the length of every line in a file to catch the single longest one, since lines over a certain length must be flagged for readability.
 Write a program that reads a whole number N, then reads N more lines (treat them as the file's contents), and prints the length of the longest line. If N is 0, print `0`.
-### Input Format
-- Line 1: N, the number of lines in the file
-- Next N lines: the file's contents
-### Output Format
-```
-3
-```
 ### Example Walkthrough
 In the sample, N is 3 and the lines are `a` (length 1), `abc` (length 3), and `ab` (length 2). The longest is `abc` with length 3, so the program prints `3`.
 ### Constraints
 - N is a valid whole number matching the number of lines that follow.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -2239,280 +2161,85 @@
       <c r="AG11" t="inlineStr">
         <is>
           <t>n=int(input()); best=0
-for _ in range(n): best=max(best,len(input()))
+for _ in range(n): best=max(best,len(input()))   # keep the longest line length seen so far
 print(best)</t>
         </is>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AH11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>explanation</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>difficulty</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>bloomTaxonomy</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>tags</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>subjects</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>topics</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>subTopics</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>companies</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>codingType</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>language</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>supportAllLanguages</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>enablePartialScore</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>ignoreCase</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>testcase1_input</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>testcase1_output</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>testcase2_input</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>testcase2_output</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>testcase3_input</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>testcase3_output</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>testcase4_input</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>testcase4_output</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>testcase5_input</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>testcase5_output</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>testcase6_input</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>testcase6_output</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>testcase7_input</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>testcase7_output</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>preloadCode_python</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>solution_python</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>hints</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Python - Log Level Counts</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-The city bus-tracking app that Farhan helps maintain writes a log file where every line starts with a level — INFO, WARN, or ERROR — followed by a message. To spot trouble quickly, Farhan wants a count of each level. Write a program that reads N and then N log lines, and prints each level that appears with its count as 'LEVEL count', one per line, sorted alphabetically by level.
-### Input Format
-- Line 1: N
-- Next N lines: 'LEVEL message'
-### Output Format
-```
-ERROR 1
-INFO 2
-```
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>The city bus-tracking app that Farhan helps maintain writes a log file where every line starts with a level — INFO, WARN, or ERROR — followed by a message. To spot trouble quickly, Farhan wants a count of each level. Write a program that reads N and then N log lines, and prints each level that appears with its count as 'LEVEL count', one per line, sorted alphabetically by level.
 ### Example Walkthrough
 The 3 sample lines have the levels INFO, ERROR, INFO — so ERROR appears once and INFO twice. Sorted alphabetically, ERROR comes before INFO, giving `ERROR 1` on the first line and `INFO 2` on the second.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>5</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>file-handling</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>file-operations</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O2" t="b">
+      <c r="O12" t="b">
         <v>0</v>
       </c>
-      <c r="P2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q2" t="b">
-        <v>1</v>
-      </c>
-      <c r="R2" t="inlineStr">
+      <c r="P12" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="b">
+        <v>1</v>
+      </c>
+      <c r="R12" t="inlineStr">
         <is>
           <t>3
 INFO started
@@ -2520,52 +2247,52 @@
 INFO done</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>ERROR 1
 INFO 2</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>2
 WARN x
 WARN y</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>WARN 2</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>1
 ERROR z</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>ERROR 1</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>1
 INFO only</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>INFO 1</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>4
 ERROR a
@@ -2574,176 +2301,168 @@
 ERROR d</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>ERROR 2
 INFO 1
 WARN 1</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>2
 INFO x
 ERROR y</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AE12" t="inlineStr">
         <is>
           <t>ERROR 1
 INFO 1</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AG12" t="inlineStr">
         <is>
           <t>n = int(input())
 counts = {}
 for _ in range(n):
-    level = input().split()[0]
+    level = input().split()[0]   # first word of each simulated log line is its level
     counts[level] = counts.get(level, 0) + 1
-for level in sorted(counts):
+for level in sorted(counts):   # alphabetical order, as required
     print(level, counts[level])</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Python - CSV to JSON</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-The alumni cell keeps member details in a CSV file — a header row followed by data rows — but the new college website needs the same data as JSON. Write a program that reads the CSV (first line is the header, remaining lines are data), turns each data row into an object using the header names as keys, and prints the whole list of objects with json.dumps. Every value stays a string, exactly as it appeared in the CSV.
-### Input Format
-- Line 1: Header row
-- Next lines: data rows
-### Output Format
-```
-[{"name": "asha", "age": "20"}, {"name": "kabir", "age": "21"}]
-```
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>The alumni cell keeps member details in a CSV file — a header row followed by data rows — but the new college website needs the same data as JSON. Write a program that reads the CSV (first line is the header, remaining lines are data), turns each data row into an object using the header names as keys, and prints the whole list of objects with json.dumps. Every value stays a string, exactly as it appeared in the CSV.
 ### Example Walkthrough
 The header `name,age` provides the keys. The row `asha,20` becomes the object {"name": "asha", "age": "20"}, and `kabir,21` becomes a similar object. json.dumps then prints both together as one JSON list.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
         <v>5</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>file-handling</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>csv-processing</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O3" t="b">
+      <c r="O13" t="b">
         <v>0</v>
       </c>
-      <c r="P3" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="b">
-        <v>1</v>
-      </c>
-      <c r="R3" t="inlineStr">
+      <c r="P13" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="b">
+        <v>1</v>
+      </c>
+      <c r="R13" t="inlineStr">
         <is>
           <t>name,age
 asha,20
 kabir,21</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>[{"name": "asha", "age": "20"}, {"name": "kabir", "age": "21"}]</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>city
 Delhi</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>[{"city": "Delhi"}]</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>a,b
 1,2
 3,4</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>[{"a": "1", "b": "2"}, {"a": "3", "b": "4"}]</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>name,age</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>x,y,z
 1,2,3</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>[{"x": "1", "y": "2", "z": "3"}]</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>a
 b
@@ -2751,147 +2470,141 @@
 d</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>[{"a": "b"}, {"a": "c"}, {"a": "d"}]</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AD13" t="inlineStr">
         <is>
           <t>col1,col2
 v1,v2</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AE13" t="inlineStr">
         <is>
           <t>[{"col1": "v1", "col2": "v2"}]</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AG13" t="inlineStr">
         <is>
           <t>import csv, json, sys
-rows = list(csv.DictReader(sys.stdin))
-print(json.dumps([dict(row) for row in rows]))</t>
+rows = list(csv.DictReader(sys.stdin))   # read CSV rows as dicts, like reading a CSV file
+print(json.dumps([dict(row) for row in rows]))   # write JSON the way json.dump() writes to a file</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Python - Numbered Lines</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Read the lines of a file and print each one prefixed by its line number starting at 1, in the form 'number: line'.
-### Input Format
-- All lines: the file contents
-### Output Format
-```
-1: apple
-2: banana
-```
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>A code-review tool at a college hackathon needs to display submitted Python files with line numbers so reviewers can point out exactly where a bug is, just like an IDE's gutter.
+Read the lines of a file and print each one prefixed by its line number starting at 1, in the form 'number: line'.
 ### Example Walkthrough
 In the sample, the lines are `apple` and `banana`. Prefixing each with its 1-based line number gives `1: apple` and `2: banana`, which the program prints.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
         <v>5</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>file-handling</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>file-operations</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O4" t="b">
+      <c r="O14" t="b">
         <v>0</v>
       </c>
-      <c r="P4" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="b">
-        <v>1</v>
-      </c>
-      <c r="R4" t="inlineStr">
+      <c r="P14" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="b">
+        <v>1</v>
+      </c>
+      <c r="R14" t="inlineStr">
         <is>
           <t>apple
 banana</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>1: apple
 2: banana</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>one</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>1: one</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>a
 b
 c</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>1: a
 2: b
 3: c</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>x
 y
@@ -2899,7 +2612,7 @@
 w</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>1: x
 2: y
@@ -2907,29 +2620,29 @@
 4: w</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>solo</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AA14" t="inlineStr">
         <is>
           <t>1: solo</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>p
 q</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AC14" t="inlineStr">
         <is>
           <t>1: p
 2: q</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AD14" t="inlineStr">
         <is>
           <t>m
 n
@@ -2938,7 +2651,7 @@
 q</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AE14" t="inlineStr">
         <is>
           <t>1: m
 2: n
@@ -2947,136 +2660,131 @@
 5: q</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
+      <c r="AG14" t="inlineStr">
         <is>
           <t>import sys
-for i, line in enumerate(sys.stdin.read().splitlines(), 1):
+for i, line in enumerate(sys.stdin.read().splitlines(), 1):   # simulate reading a file's lines, numbered
     print(f"{i}: {line}")</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Python - Word Count of a File</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Read all lines of a file and print the total number of words across every line.
-### Input Format
-- All lines: the file contents
-### Output Format
-```
-4
-```
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>A college writing centre built a tool that checks whether a student's submitted essay file meets the minimum word count before it accepts the submission.
+Read all lines of a file and print the total number of words across every line.
 ### Example Walkthrough
 In the sample, the lines are `the quick` and `brown fox`. Together they contain `4` words, so the program prints `4`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
         <v>5</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>file-handling</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>file-operations</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O5" t="b">
+      <c r="O15" t="b">
         <v>0</v>
       </c>
-      <c r="P5" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="b">
-        <v>1</v>
-      </c>
-      <c r="R5" t="inlineStr">
+      <c r="P15" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="b">
+        <v>1</v>
+      </c>
+      <c r="R15" t="inlineStr">
         <is>
           <t>the quick
 brown fox</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>hello</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>a b
 c d e</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>one</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>a
 b
@@ -3084,343 +2792,332 @@
 d</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AA15" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t xml:space="preserve">  spaced   words  </t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AC15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AD15" t="inlineStr">
         <is>
           <t>x y z
 p q</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AE15" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AG15" t="inlineStr">
         <is>
           <t>import sys
-text = sys.stdin.read()
+text = sys.stdin.read()   # read all input at once, as if it were a file's full contents
 print(len(text.split()))</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Python - File Name from Path</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Use pathlib to read a file path and print just the final file name.
-### Input Format
-- Line 1: A file path
-### Output Format
-```
-file.txt
-```
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>A file-organizer app scans full folder paths sent from a backup service and needs to show the user just the file name, not the whole directory trail, when listing recovered files.
+Use pathlib to read a file path and print just the final file name.
 ### Example Walkthrough
-In the sample, the path is `home/user/file.txt`. The final component is `file.txt`, which the program prints.
+In the sample, the path is `/home/user/file.txt`. The final component is `file.txt`, which the program prints.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
         <v>5</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>file-handling</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>file-paths</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O6" t="b">
+      <c r="O16" t="b">
         <v>0</v>
       </c>
-      <c r="P6" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q6" t="b">
-        <v>1</v>
-      </c>
-      <c r="R6" t="inlineStr">
+      <c r="P16" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="b">
+        <v>1</v>
+      </c>
+      <c r="R16" t="inlineStr">
         <is>
           <t>/home/user/file.txt</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>file.txt</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>docs/report.pdf</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>report.pdf</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>data.csv</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>data.csv</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>file.txt</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>file.txt</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>/a/b/c/d.py</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AA16" t="inlineStr">
         <is>
           <t>d.py</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>/trailing/slash/dir/</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AC16" t="inlineStr">
         <is>
           <t>dir</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AD16" t="inlineStr">
         <is>
           <t>/x/y/z/report.final.csv</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AE16" t="inlineStr">
         <is>
           <t>report.final.csv</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AG16" t="inlineStr">
         <is>
           <t>from pathlib import PurePosixPath
-print(PurePosixPath(input()).name)</t>
+print(PurePosixPath(input()).name)   # pathlib pulls out just the final path component</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Python - Shout the File</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Read the lines of a file and print each line converted to upper case.
-### Input Format
-- All lines: the file contents
-### Output Format
-```
-HELLO
-WORLD
-```
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>A text-to-speech accessibility app has a 'shout mode' that displays each caption in upper case so it stands out on screen while the line is read aloud with extra emphasis.
+Read the lines of a file and print each line converted to upper case.
 ### Example Walkthrough
 In the sample, the lines are `hello` and `world`. Converting each to upper case gives `HELLO` and `WORLD`, which the program prints one per line.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
         <v>5</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>file-handling</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>file-operations</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O7" t="b">
+      <c r="O17" t="b">
         <v>0</v>
       </c>
-      <c r="P7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q7" t="b">
-        <v>1</v>
-      </c>
-      <c r="R7" t="inlineStr">
+      <c r="P17" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="b">
+        <v>1</v>
+      </c>
+      <c r="R17" t="inlineStr">
         <is>
           <t>hello
 world</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>HELLO
 WORLD</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>abc</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>a
 b</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>A
 B</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>MiXeD case</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>MIXED CASE</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>already UPPER</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AA17" t="inlineStr">
         <is>
           <t>ALREADY UPPER</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>1 2 3
 four</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AC17" t="inlineStr">
         <is>
           <t>1 2 3
 FOUR</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AD17" t="inlineStr">
         <is>
           <t>x
 y
@@ -3428,7 +3125,7 @@
 w</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AE17" t="inlineStr">
         <is>
           <t>X
 Y
@@ -3436,149 +3133,144 @@
 W</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AG17" t="inlineStr">
         <is>
           <t>import sys
-for line in sys.stdin.read().splitlines():
+for line in sys.stdin.read().splitlines():   # treat each input line as one line of a file
     print(line.upper())</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Python - Character Count</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Read the lines of a file and print how many characters there are in total, not counting the line breaks.
-### Input Format
-- All lines: the file contents
-### Output Format
-```
-5
-```
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>An SMS character-limit checker needs to know exactly how many characters a multi-line draft message contains, excluding the line breaks themselves, before warning the user it is too long to send as one text.
+Read the lines of a file and print how many characters there are in total, not counting the line breaks.
 ### Example Walkthrough
-In the sample, the only line is `hello`, which has `5` characters, so the program prints `5`.
+In the sample, the lines are `abc` and `de`. Together they have `5` characters (`3` from `abc` and `2` from `de`), so the program prints `5`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
         <v>5</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>file-handling</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>file-operations</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O8" t="b">
+      <c r="O18" t="b">
         <v>0</v>
       </c>
-      <c r="P8" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="b">
-        <v>1</v>
-      </c>
-      <c r="R8" t="inlineStr">
+      <c r="P18" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="b">
+        <v>1</v>
+      </c>
+      <c r="R18" t="inlineStr">
         <is>
           <t>abc
 de</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>hello</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>a
 b
 c</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>ab
 cd
 ef</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AA18" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AB18" t="inlineStr">
         <is>
           <t>one
 two
@@ -3586,158 +3278,151 @@
 four</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AC18" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AD18" t="inlineStr">
         <is>
           <t xml:space="preserve">  spaced  
 line</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AE18" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AG18" t="inlineStr">
         <is>
           <t>import sys
-lines = sys.stdin.read().splitlines()
+lines = sys.stdin.read().splitlines()   # splitlines drops newline characters, like reading file lines
 print(sum(len(line) for line in lines))</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Python - Reverse the Lines</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Read the lines of a file and print them in reverse order (last line first).
-### Input Format
-- All lines: the file contents
-### Output Format
-```
-c
-b
-a
-```
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>A note-taking app's 'read backwards' accessibility feature lets a user review their most recent journal entries first by displaying the lines of a saved file in reverse order.
+Read the lines of a file and print them in reverse order (last line first).
 ### Example Walkthrough
 In the sample, the lines are `a`, `b`, and `c`. Printed in reverse order, they become `c`, `b`, and `a`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
         <v>5</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>file-handling</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>file-operations</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O9" t="b">
+      <c r="O19" t="b">
         <v>0</v>
       </c>
-      <c r="P9" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="b">
-        <v>1</v>
-      </c>
-      <c r="R9" t="inlineStr">
+      <c r="P19" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q19" t="b">
+        <v>1</v>
+      </c>
+      <c r="R19" t="inlineStr">
         <is>
           <t>a
 b
 c</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>c
 b
 a</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>one</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>one</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>x
 y</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y
 x</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>p
 q
@@ -3745,7 +3430,7 @@
 s</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AA19" t="inlineStr">
         <is>
           <t>s
 r
@@ -3753,619 +3438,415 @@
 p</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AB19" t="inlineStr">
         <is>
           <t>z</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AC19" t="inlineStr">
         <is>
           <t>z</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AD19" t="inlineStr">
         <is>
           <t>m
 n
 o</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AE19" t="inlineStr">
         <is>
           <t>o
 n
 m</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AG19" t="inlineStr">
         <is>
           <t>import sys
-lines = sys.stdin.read().splitlines()
+lines = sys.stdin.read().splitlines()   # simulate reading all lines of a file into memory
 for line in reversed(lines):
     print(line)</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Python - Path Extension</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>A media library organizes uploaded files by type using the text after the last dot in the file name, but some files are uploaded with no dot at all and need special handling.
 Write a program that reads a file name and prints the text after the last `.` in the name (without the dot itself). If the name has no dot, print `none`.
-### Input Format
-- Line 1: A file name
-### Output Format
-```
-txt
-```
 ### Example Walkthrough
 In the sample, the file name is `a.txt`. The text after the last dot is `txt`, so the program prints `txt`. A name with no dot, like `README`, would print `none`.
 ### Constraints
 - The input is a valid file name with no spaces.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
         <v>5</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>file-handling</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>file-paths</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O10" t="b">
+      <c r="O20" t="b">
         <v>0</v>
       </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="b">
-        <v>1</v>
-      </c>
-      <c r="R10" t="inlineStr">
+      <c r="P20" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="b">
+        <v>1</v>
+      </c>
+      <c r="R20" t="inlineStr">
         <is>
           <t>a.txt</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>txt</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>data.csv</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>csv</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>README</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>archive.tar.gz</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>gz</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>/tmp/x.py</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AA20" t="inlineStr">
         <is>
           <t>py</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB20" t="inlineStr">
         <is>
           <t>no.dot</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC20" t="inlineStr">
         <is>
           <t>dot</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AD20" t="inlineStr">
         <is>
           <t>image.PNG</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AE20" t="inlineStr">
         <is>
           <t>PNG</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>name=input(); print(name.split(".")[-1] if "." in name else "none")</t>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>name=input()
+print(name.split(".")[-1] if "." in name else "none")   # text after the last dot, like a file extension</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Python - CSV Column Count</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>A CSV import validator checks how many columns each row of a spreadsheet export has, to make sure every row matches the expected column count before the data is processed further.
 Write a program that reads one line representing a CSV row (values separated by commas) and prints how many columns it has. If the line is empty, print `0`.
-### Input Format
-- Line 1: A CSV row (comma-separated values)
-### Output Format
-```
-3
-```
 ### Example Walkthrough
 In the sample, the row is `a,b,c`. Splitting on commas gives three values, so the program prints `3`.
 ### Constraints
 - The input is a single valid line representing one CSV row.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
         <v>5</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>easy</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>python - Set 2</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>file-handling</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>csv-processing</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O11" t="b">
+      <c r="O21" t="b">
         <v>0</v>
       </c>
-      <c r="P11" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="b">
-        <v>1</v>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="P21" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="b">
+        <v>1</v>
+      </c>
+      <c r="R21" t="inlineStr">
         <is>
           <t>a,b,c</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>one</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>1,2</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>x,y,z,w</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>blank</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AA21" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB21" t="inlineStr">
         <is>
           <t>name,age,city</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC21" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AD21" t="inlineStr">
         <is>
           <t>a,,b</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AE21" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>row=input(); print(0 if row=="" else len(row.split(",")))</t>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>row=input(); print(0 if row=="" else len(row.split(",")))   # count comma-separated fields in a CSV row</t>
         </is>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AH11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>explanation</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>difficulty</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>bloomTaxonomy</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>tags</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>subjects</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>topics</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>subTopics</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>companies</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>codingType</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>language</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>supportAllLanguages</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>enablePartialScore</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>ignoreCase</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>testcase1_input</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>testcase1_output</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>testcase2_input</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>testcase2_output</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>testcase3_input</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>testcase3_output</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>testcase4_input</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>testcase4_output</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>testcase5_input</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>testcase5_output</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>testcase6_input</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>testcase6_output</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>testcase7_input</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>testcase7_output</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>preloadCode_python</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>solution_python</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>hints</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Python - Filter CSV Rows</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>A CSV file has a header 'name,score'. Use csv.DictReader to print the names of everyone scoring 40 or more, one per line.
-### Input Format
-- Line 1: Header 'name,score'
-- Next lines: data rows
-### Output Format
-```
-asha
-meera
-```
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>A college exam cell keeps a CSV of every student's score and needs to quickly pull out the names of students who cleared the 40-mark passing threshold for the department noticeboard.
+A CSV file has a header 'name,score'. Use csv.DictReader to print the names of everyone scoring 40 or more, one per line.
 ### Example Walkthrough
-In the sample, the rows are `asha,80`, `kabir,30`, and `meera,50`. Only `asha` and `meera` score `40` or more, so the program prints `asha` then `meera`.
+In the sample, the rows are `asha,80`, `kabir,30`, and `meera,55`. Only `asha` and `meera` score `40` or more, so the program prints `asha` then `meera`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
         <v>5</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>file-handling</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>csv-processing</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O2" t="b">
+      <c r="O22" t="b">
         <v>0</v>
       </c>
-      <c r="P2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q2" t="b">
-        <v>1</v>
-      </c>
-      <c r="R2" t="inlineStr">
+      <c r="P22" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q22" t="b">
+        <v>1</v>
+      </c>
+      <c r="R22" t="inlineStr">
         <is>
           <t>name,score
 asha,80
@@ -4373,48 +3854,48 @@
 meera,55</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>asha
 meera</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>name,score
 sam,40</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>sam</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>name,score
 a,90
 b,20</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>name,score
 x,39</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>name,score
 y,0</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB22" t="inlineStr">
         <is>
           <t>name,score
 a,40
@@ -4422,110 +3903,102 @@
 c,40</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AC22" t="inlineStr">
         <is>
           <t>a
 b
 c</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AD22" t="inlineStr">
         <is>
           <t>name,score</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AG22" t="inlineStr">
         <is>
           <t>import csv, sys
-for row in csv.DictReader(sys.stdin):
+for row in csv.DictReader(sys.stdin):   # DictReader reads CSV rows as dicts keyed by header
     if int(row["score"]) &gt;= 40:
         print(row["name"])</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Python - Match by Extension</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Read N file names, then an extension (without the dot). Print the file names that end with that extension, in order, one per line.
-### Input Format
-- Line 1: N
-- Next N lines: file names
-- Last line: an extension
-### Output Format
-```
-a.txt
-c.txt
-```
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>A file-organizer app is cleaning up a messy Downloads folder and needs to pull out just the files of one particular type the user wants to move into a dedicated folder.
+Read N file names, then an extension (without the dot). Print the file names that end with that extension, in order, one per line.
 ### Example Walkthrough
-In the sample, the file names are `a.txt`, `b.md`, and `c.txt`, and the extension to match is `txt`. Only `a.txt` and `c.txt` end with `.txt`, so the program prints them in order.
+In the sample, the file names are `a.txt`, `b.py`, and `c.txt`, and the extension to match is `txt`. Only `a.txt` and `c.txt` end with `.txt`, so the program prints them in order.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
         <v>5</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>file-handling</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>file-paths</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O3" t="b">
+      <c r="O23" t="b">
         <v>0</v>
       </c>
-      <c r="P3" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="b">
-        <v>1</v>
-      </c>
-      <c r="R3" t="inlineStr">
+      <c r="P23" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q23" t="b">
+        <v>1</v>
+      </c>
+      <c r="R23" t="inlineStr">
         <is>
           <t>3
 a.txt
@@ -4534,13 +4007,13 @@
 txt</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>a.txt
 c.txt</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>2
 x.md
@@ -4548,13 +4021,13 @@
 md</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>x.md
 y.md</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>2
 p.jpg
@@ -4562,30 +4035,30 @@
 jpg</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>p.jpg</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>0
 txt</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>1
 file.txt
 txt</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA23" t="inlineStr">
         <is>
           <t>file.txt</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AB23" t="inlineStr">
         <is>
           <t>3
 a.txt
@@ -4594,7 +4067,7 @@
 py</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AD23" t="inlineStr">
         <is>
           <t>4
 a.py
@@ -4604,104 +4077,98 @@
 py</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AE23" t="inlineStr">
         <is>
           <t>a.py
 c.py</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AG23" t="inlineStr">
         <is>
           <t>n = int(input())
-names = [input() for _ in range(n)]
+names = [input() for _ in range(n)]   # simulate reading a list of file names
 ext = input()
 for name in names:
-    if name.endswith("." + ext):
+    if name.endswith("." + ext):   # simple suffix check in place of pathlib
         print(name)</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Python - Build a Path</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Read N path segments and join them into a single path using pathlib, printing the result with '/' separators.
-### Input Format
-- Line 1: N
-- Next N lines: one path segment each
-### Output Format
-```
-home/user/file.txt
-```
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>The same file-organizer app needs to construct the destination path for a file it is about to move, by joining a folder name, a subfolder name, and a file name together correctly.
+Read N path segments and join them into a single path using pathlib, printing the result with '/' separators.
 ### Example Walkthrough
 In the sample, the segments are `home`, `user`, and `file.txt`. Joined together with `/`, they form `home/user/file.txt`, which the program prints.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
         <v>5</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>file-handling</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>file-paths</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O4" t="b">
+      <c r="O24" t="b">
         <v>0</v>
       </c>
-      <c r="P4" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="b">
-        <v>1</v>
-      </c>
-      <c r="R4" t="inlineStr">
+      <c r="P24" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q24" t="b">
+        <v>1</v>
+      </c>
+      <c r="R24" t="inlineStr">
         <is>
           <t>3
 home
@@ -4709,35 +4176,35 @@
 file.txt</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>home/user/file.txt</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>2
 docs
 a.pdf</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>docs/a.pdf</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>1
 readme</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>readme</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>4
 a
@@ -4746,35 +4213,35 @@
 d.txt</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>a/b/c/d.txt</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>1
 single</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AA24" t="inlineStr">
         <is>
           <t>single</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AB24" t="inlineStr">
         <is>
           <t>2
 x
 y</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AC24" t="inlineStr">
         <is>
           <t>x/y</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AD24" t="inlineStr">
         <is>
           <t>3
 p
@@ -4782,168 +4249,163 @@
 r</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AE24" t="inlineStr">
         <is>
           <t>p/q/r</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
+      <c r="AG24" t="inlineStr">
         <is>
           <t>from pathlib import PurePosixPath
 n = int(input())
-parts = [input() for _ in range(n)]
-print(PurePosixPath(*parts))</t>
+parts = [input() for _ in range(n)]   # each part simulates one path segment
+print(PurePosixPath(*parts))   # pathlib joins segments with the right separator</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Python - Longest Line</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Read the lines of a file and print the longest line. If several lines tie for longest, print the one that appears first.
-### Input Format
-- All lines: the file contents
-### Output Format
-```
-bbb
-```
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>A quotes app scans a text file of saved quotes and highlights the single longest one on the home screen banner, since it makes the boldest visual statement.
+Read the lines of a file and print the longest line. If several lines tie for longest, print the one that appears first.
 ### Example Walkthrough
 In the sample, the lines are `a`, `bbb`, and `cc`. The longest is `bbb`, so the program prints `bbb`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
         <v>5</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>file-handling</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>file-operations</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O5" t="b">
+      <c r="O25" t="b">
         <v>0</v>
       </c>
-      <c r="P5" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="b">
-        <v>1</v>
-      </c>
-      <c r="R5" t="inlineStr">
+      <c r="P25" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q25" t="b">
+        <v>1</v>
+      </c>
+      <c r="R25" t="inlineStr">
         <is>
           <t>a
 bbb
 cc</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>bbb</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>hello</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>hello</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>one
 two
 three</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>three</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>aa
 bb
 cc</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AA25" t="inlineStr">
         <is>
           <t>aa</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AB25" t="inlineStr">
         <is>
           <t>short
 reallylongline
 med</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AC25" t="inlineStr">
         <is>
           <t>reallylongline</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AD25" t="inlineStr">
         <is>
           <t>z
 zz
@@ -4951,276 +4413,263 @@
 zz</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AE25" t="inlineStr">
         <is>
           <t>zzz</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AG25" t="inlineStr">
         <is>
           <t>import sys
-lines = sys.stdin.read().splitlines()
+lines = sys.stdin.read().splitlines()   # simulate reading all lines of a file
 best = lines[0]
 for line in lines[1:]:
-    if len(line) &gt; len(best):
+    if len(line) &gt; len(best):   # keep the first line seen among ties
         best = line
 print(best)</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Python - Count a Word in a File</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>The first line is a word to search for. The remaining lines are the file contents. Print how many times the word appears across those lines.
-### Input Format
-- Line 1: The word to search for
-- Remaining lines: file contents
-### Output Format
-```
-3
-```
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>A writing-lab keyword scanner checks how often a student overuses a particular word in their submitted essay file, starting with the word to look for on the first line, followed by the essay text itself.
+The first line is a word to search for. The remaining lines are the file contents. Print how many times the word appears across those lines.
 ### Example Walkthrough
-In the sample, the word to find is `cat`, and the remaining lines are `cat dog cat` and `cat bird`. The word `cat` appears `3` times in total, so the program prints `3`.
+In the sample, the word to find is `cat`, and the remaining lines are `the cat sat` and `cat and cat`. The word `cat` appears `3` times in total, so the program prints `3`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
         <v>5</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>file-handling</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>file-operations</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O6" t="b">
+      <c r="O26" t="b">
         <v>0</v>
       </c>
-      <c r="P6" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q6" t="b">
-        <v>1</v>
-      </c>
-      <c r="R6" t="inlineStr">
+      <c r="P26" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q26" t="b">
+        <v>1</v>
+      </c>
+      <c r="R26" t="inlineStr">
         <is>
           <t>cat
 the cat sat
 cat and cat</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>x
 x y x
 z</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>hi
 hello
 world</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>missing
 a b c</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Y26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="Z26" t="inlineStr">
         <is>
           <t>cat
 catapult cat</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AA26" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AB26" t="inlineStr">
         <is>
           <t>a
 a a a
 a a</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AC26" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AD26" t="inlineStr">
         <is>
           <t>dog
 no match here</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AE26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AG26" t="inlineStr">
         <is>
           <t>import sys
-lines = sys.stdin.read().splitlines()
+lines = sys.stdin.read().splitlines()   # simulate reading a file: first line is the search word
 word = lines[0]
-body = " ".join(lines[1:]).split()
+body = " ".join(lines[1:]).split()   # remaining lines are the file body, split into words
 print(body.count(word))</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>Python - Unique Lines</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Read the lines of a file and print each distinct line once, keeping the order of first appearance.
-### Input Format
-- All lines: the file contents
-### Output Format
-```
-a
-b
-c
-```
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>A college club exported its mailing list to a text file, but some email IDs got added twice by accident, and the volunteer sending the newsletter needs a clean list with each address kept only once, in the order it first appeared.
+Read the lines of a file and print each distinct line once, keeping the order of first appearance.
 ### Example Walkthrough
-In the sample, the lines are `a`, `a`, `b`, `c`, and `b`. Keeping only the first occurrence of each gives `a`, `b`, and `c`, in that order.
+In the sample, the lines are `a`, `b`, `a`, `c`, and `b`. Keeping only the first occurrence of each gives `a`, `b`, and `c`, in that order.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
         <v>5</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>file-handling</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>file-operations</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O7" t="b">
+      <c r="O27" t="b">
         <v>0</v>
       </c>
-      <c r="P7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q7" t="b">
-        <v>1</v>
-      </c>
-      <c r="R7" t="inlineStr">
+      <c r="P27" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="b">
+        <v>1</v>
+      </c>
+      <c r="R27" t="inlineStr">
         <is>
           <t>a
 b
@@ -5229,45 +4678,45 @@
 b</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>a
 b
 c</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="V27" t="inlineStr">
         <is>
           <t>one
 one</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>one</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Y27" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="Z27" t="inlineStr">
         <is>
           <t>a
 a
@@ -5275,12 +4724,12 @@
 a</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AA27" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AB27" t="inlineStr">
         <is>
           <t>p
 q
@@ -5289,212 +4738,204 @@
 q</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AC27" t="inlineStr">
         <is>
           <t>p
 q
 r</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AD27" t="inlineStr">
         <is>
           <t>z
 y
 x</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AE27" t="inlineStr">
         <is>
           <t>z
 y
 x</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AG27" t="inlineStr">
         <is>
           <t>import sys
 seen = []
-for line in sys.stdin.read().splitlines():
-    if line not in seen:
+for line in sys.stdin.read().splitlines():   # simulate scanning a file line by line
+    if line not in seen:   # keep only the first occurrence of each line
         seen.append(line)
 for line in seen:
     print(line)</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Python - Student Report CSV</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>A CSV has header 'name,m1,m2,m3' and data rows. Print a new CSV with header 'name,total,average', where average is rounded to 1 decimal place, one row per student.
-### Input Format
-- Line 1: Header 'name,`m1`,`m2`,`m3`'
-- Next lines: data rows
-### Output Format
-```
-name,total,average
-asha,270,90.0
-kabir,180,60.0
-```
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>A school's report-card generator reads each student's marks in three subjects from a CSV export and produces a summary CSV showing each student's total and average, ready to print on the report card.
+A CSV has header 'name,m1,m2,m3' and data rows. Print a new CSV with header 'name,total,average', where average is rounded to 1 decimal place, one row per student.
 ### Example Walkthrough
-In the sample, `asha` has marks `90, 90, 90` (total `270`, average `90.0`), and `kabir` has marks `60, 60, 60` (total `180`, average `60.0`), so the program prints the header followed by both rows.
+In the sample, `asha` has marks `80, 90, 100` (total `270`, average `90.0`), and `kabir` has marks `60, 60, 60` (total `180`, average `60.0`), so the program prints the header followed by both rows.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
         <v>5</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>file-handling</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>csv-processing</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O8" t="b">
+      <c r="O28" t="b">
         <v>0</v>
       </c>
-      <c r="P8" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="b">
-        <v>1</v>
-      </c>
-      <c r="R8" t="inlineStr">
+      <c r="P28" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q28" t="b">
+        <v>1</v>
+      </c>
+      <c r="R28" t="inlineStr">
         <is>
           <t>name,m1,m2,m3
 asha,80,90,100
 kabir,60,60,60</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>name,total,average
 asha,270,90.0
 kabir,180,60.0</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>name,m1,m2,m3
 sam,50,50,50</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>name,total,average
 sam,150,50.0</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V28" t="inlineStr">
         <is>
           <t>name,m1,m2,m3
 a,10,20,30</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>name,total,average
 a,60,20.0</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>name,m1,m2,m3
 zed,0,0,0</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Y28" t="inlineStr">
         <is>
           <t>name,total,average
 zed,0,0.0</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="Z28" t="inlineStr">
         <is>
           <t>name,m1,m2,m3
 x,100,100,100</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AA28" t="inlineStr">
         <is>
           <t>name,total,average
 x,300,100.0</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AB28" t="inlineStr">
         <is>
           <t>name,m1,m2,m3
 p,1,2,2
 q,3,3,3</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AC28" t="inlineStr">
         <is>
           <t>name,total,average
 p,5,1.7
 q,9,3.0</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AD28" t="inlineStr">
         <is>
           <t>name,m1,m2,m3</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AE28" t="inlineStr">
         <is>
           <t>name,total,average</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AG28" t="inlineStr">
         <is>
           <t>import csv, sys
-reader = csv.DictReader(sys.stdin)
-writer = csv.writer(sys.stdout)
+reader = csv.DictReader(sys.stdin)   # read CSV rows as dicts, like reading a CSV file
+writer = csv.writer(sys.stdout)   # write output rows the way csv.writer writes to a file
 writer.writerow(["name", "total", "average"])
 for row in reader:
     marks = [int(row["m1"]), int(row["m2"]), int(row["m3"])]
@@ -5504,450 +4945,429 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Python - JSON Key Value</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>A config loader reads a single JSON object representing an app's settings and needs to fetch one setting by name, reporting `Missing` if that setting isn't present in the file.
 Write a program that reads a line of JSON representing an object, parses it, reads a key on the next line, and prints the value for that key if it exists, or `Missing` otherwise.
-### Input Format
-- Line 1: A JSON object
-- Line 2: The key to look up
-### Output Format
-```
-Asha
-```
 ### Example Walkthrough
 In the sample, the JSON is `{"name":"Asha","age":19}` and the key is `name`. Looking up `name` in the parsed object gives `Asha`, so the program prints `Asha`.
 ### Constraints
 - The input is valid JSON representing an object.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
         <v>5</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>file-handling</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>json-processing</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O9" t="b">
+      <c r="O29" t="b">
         <v>0</v>
       </c>
-      <c r="P9" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="b">
-        <v>1</v>
-      </c>
-      <c r="R9" t="inlineStr">
+      <c r="P29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q29" t="b">
+        <v>1</v>
+      </c>
+      <c r="R29" t="inlineStr">
         <is>
           <t>{"name":"Asha","age":19}
 name</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>Asha</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>{"x":5}
 y</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V29" t="inlineStr">
         <is>
           <t>{}
 a</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="W29" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>{"city":"Pune"}
 city</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Y29" t="inlineStr">
         <is>
           <t>Pune</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="Z29" t="inlineStr">
         <is>
           <t>{"a":1,"b":2}
 b</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AA29" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AB29" t="inlineStr">
         <is>
           <t>{"ok":true}
 ok</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AC29" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AD29" t="inlineStr">
         <is>
           <t>{"v":null}
 v</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AE29" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AG29" t="inlineStr">
         <is>
           <t>import json
-d=json.loads(input()); k=input(); print(d.get(k,"Missing"))</t>
+d=json.loads(input()); k=input(); print(d.get(k,"Missing"))   # parse JSON, then look up a key like a config file</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>Python - Glob Suffix Match</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>A backup tool scans a folder's file list to count how many files match a certain extension pattern (like a simplified `*.py` glob), to decide whether a backup step is needed for that file type.
 Write a program that reads a line of space-separated file names, reads a suffix on the next line, and prints how many of the file names end with that exact suffix.
-### Input Format
-- Line 1: Space-separated file names
-- Line 2: A suffix (e.g. `.py`)
-### Output Format
-```
-2
-```
 ### Example Walkthrough
 In the sample, the file names are `a.py b.txt c.py` and the suffix is `.py`. Two of the three file names (`a.py` and `c.py`) end with `.py`, so the program prints `2`.
 ### Constraints
 - The inputs are valid, non-empty lines of text.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
         <v>5</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>file-handling</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>glob-pattern-matching</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O10" t="b">
+      <c r="O30" t="b">
         <v>0</v>
       </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="b">
-        <v>1</v>
-      </c>
-      <c r="R10" t="inlineStr">
+      <c r="P30" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q30" t="b">
+        <v>1</v>
+      </c>
+      <c r="R30" t="inlineStr">
         <is>
           <t>a.py b.txt c.py
 .py</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>one.csv two.csv
 .csv</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V30" t="inlineStr">
         <is>
           <t>README test.md
 .md</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="W30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>a b
 .py</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Y30" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z30" t="inlineStr">
         <is>
           <t>x.JSON y.json
 .json</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AA30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB30" t="inlineStr">
         <is>
           <t>data1.txt data2.csv
 .txt</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AD30" t="inlineStr">
         <is>
           <t>main.py
 .py</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AE30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>names=input().split(); suffix=input(); print(sum(1 for n in names if n.endswith(suffix)))</t>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>names=input().split(); suffix=input(); print(sum(1 for n in names if n.endswith(suffix)))   # count names matching a suffix, like a simple glob</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Python - Context Summary</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>A document analytics tool reads through a file's contents (opened safely with a `with` statement so it always closes properly) and needs to report the total number of characters across all its lines, not counting the line breaks between them.
 Write a program that reads a whole number N, then reads N more lines (treat them as the file's contents), and prints the total number of characters across all N lines combined. If N is 0, print `0`.
-### Input Format
-- Line 1: N, the number of lines in the file
-- Next N lines: the file's contents
-### Output Format
-```
-4
-```
 ### Example Walkthrough
 In the sample, N is 2 and the lines are `ab` (2 characters) and `cd` (2 characters). Adding their lengths gives 2 + 2 = 4, so the program prints `4`.
 ### Constraints
 - N is a valid whole number matching the number of lines that follow.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
         <v>5</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>python - Set 3</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>file-handling</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>context-managed-files</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O11" t="b">
+      <c r="O31" t="b">
         <v>0</v>
       </c>
-      <c r="P11" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="b">
-        <v>1</v>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="P31" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q31" t="b">
+        <v>1</v>
+      </c>
+      <c r="R31" t="inlineStr">
         <is>
           <t>2
 ab
 cd</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>1
 hello</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>3
 a
@@ -5955,34 +5375,34 @@
 ccc</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y31" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z31" t="inlineStr">
         <is>
           <t>2
 abc</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AA31" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB31" t="inlineStr">
         <is>
           <t xml:space="preserve">1
  </t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC31" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AD31" t="inlineStr">
         <is>
           <t>4
 x
@@ -5991,610 +5411,407 @@
 w</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AE31" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
+      <c r="AG31" t="inlineStr">
         <is>
           <t>n=int(input()); total=0
-for _ in range(n): total+=len(input())
+for _ in range(n): total+=len(input())   # add up line lengths, like reading a file opened with `with`
 print(total)</t>
         </is>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AH11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>explanation</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>difficulty</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>bloomTaxonomy</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>tags</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>subjects</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>topics</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>subTopics</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>companies</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>codingType</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>language</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>supportAllLanguages</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>enablePartialScore</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>ignoreCase</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>testcase1_input</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>testcase1_output</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>testcase2_input</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>testcase2_output</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>testcase3_input</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>testcase3_output</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>testcase4_input</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>testcase4_output</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>testcase5_input</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>testcase5_output</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>testcase6_input</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>testcase6_output</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>testcase7_input</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>testcase7_output</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>preloadCode_python</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>solution_python</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>hints</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Python - Sum JSON Values</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Read one line of JSON describing an object that maps names to numbers, and print the total of all the values.
-### Input Format
-- Line 1: A JSON object of name to number
-### Output Format
-```
-60
-```
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>A budgeting app lets users export their monthly spending by category as a JSON object, and the app's summary screen needs to show the total amount spent across all categories.
+Read one line of JSON describing an object that maps names to numbers, and print the total of all the values.
 ### Example Walkthrough
-In the sample, the JSON object is `{"a": 20, "b": 40}`. Adding its values gives `20 + 40 = 60`, so the program prints `60`.
+In the sample, the JSON object is `{"a": 10, "b": 20, "c": 30}`. Adding its values gives `10 + 20 + 30 = 60`, so the program prints `60`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
         <v>5</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>file-handling</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>json-processing</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O2" t="b">
+      <c r="O32" t="b">
         <v>0</v>
       </c>
-      <c r="P2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q2" t="b">
-        <v>1</v>
-      </c>
-      <c r="R2" t="inlineStr">
+      <c r="P32" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q32" t="b">
+        <v>1</v>
+      </c>
+      <c r="R32" t="inlineStr">
         <is>
           <t>{"a": 10, "b": 20, "c": 30}</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>{"x": 5}</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>{"p": 1, "q": 2}</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="W32" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Y32" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="Z32" t="inlineStr">
         <is>
           <t>{"neg": -10, "pos": 10}</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AA32" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB32" t="inlineStr">
         <is>
           <t>{"z": 0}</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AC32" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AD32" t="inlineStr">
         <is>
           <t>{"m": 100, "n": 200, "o": 300}</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AE32" t="inlineStr">
         <is>
           <t>600</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AG32" t="inlineStr">
         <is>
           <t>import json
-data = json.loads(input())
+data = json.loads(input())   # parse text the same way json.load() would read from an open file
 print(sum(data.values()))</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>Python - Most Common Word in File</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Read all the lines of a file and print the word that appears most often across the whole file. If several tie, print the one that appears first.
-### Input Format
-- All lines: the file contents
-### Output Format
-```
-the
-```
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>A writing-lab tool flags the single most overused word in a student's essay file so the student can revise for variety before submitting the final draft.
+Read all the lines of a file and print the word that appears most often across the whole file. If several tie, print the one that appears first.
 ### Example Walkthrough
-In the sample, the line is `the cat the dog the bird`. The word `the` appears `3` times, more than any other word, so the program prints `the`.
+In the sample, the lines are `the cat`, `the dog`, and `the`. The word `the` appears `3` times, more than any other word, so the program prints `the`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
         <v>5</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>file-handling</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>file-operations</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O3" t="b">
+      <c r="O33" t="b">
         <v>0</v>
       </c>
-      <c r="P3" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="b">
-        <v>1</v>
-      </c>
-      <c r="R3" t="inlineStr">
+      <c r="P33" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q33" t="b">
+        <v>1</v>
+      </c>
+      <c r="R33" t="inlineStr">
         <is>
           <t>the cat
 the dog
 the</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>the</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>hello world</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>hello</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V33" t="inlineStr">
         <is>
           <t>a b a</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="W33" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>solo</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Y33" t="inlineStr">
         <is>
           <t>solo</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Z33" t="inlineStr">
         <is>
           <t>x y x y</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA33" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AB33" t="inlineStr">
         <is>
           <t>one two three</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AC33" t="inlineStr">
         <is>
           <t>one</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AD33" t="inlineStr">
         <is>
           <t>cat dog cat bird cat</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AE33" t="inlineStr">
         <is>
           <t>cat</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AG33" t="inlineStr">
         <is>
           <t>import sys
-words = sys.stdin.read().split()
+words = sys.stdin.read().split()   # simulate reading a whole file and splitting it into words
 counts = {}
 for w in words:
     counts[w] = counts.get(w, 0) + 1
 best = max(counts.values())
 for w in words:
-    if counts[w] == best:
+    if counts[w] == best:   # first word to reach the max count wins ties
         print(w)
         break</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Python - Group CSV by Category</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>A CSV has header 'category,amount'. Print each category's total as 'category:total', with categories sorted alphabetically.
-### Input Format
-- Line 1: Header 'category,amount'
-- Next lines: data rows
-### Output Format
-```
-food:130
-travel:50
-```
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>A hostel expense-tracking app exports every purchase as a CSV of category and amount, and the monthly summary screen needs each category's total spend listed alphabetically.
+A CSV has header 'category,amount'. Print each category's total as 'category:total', with categories sorted alphabetically.
 ### Example Walkthrough
 In the sample, the rows are `food,100`, `travel,50`, and `food,30`. The `food` entries total `130` and `travel` totals `50`, so the program prints `food:130` then `travel:50`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
         <v>5</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>file-handling</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>csv-processing</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O4" t="b">
+      <c r="O34" t="b">
         <v>0</v>
       </c>
-      <c r="P4" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="b">
-        <v>1</v>
-      </c>
-      <c r="R4" t="inlineStr">
+      <c r="P34" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q34" t="b">
+        <v>1</v>
+      </c>
+      <c r="R34" t="inlineStr">
         <is>
           <t>category,amount
 food,100
@@ -6602,64 +5819,64 @@
 food,30</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>food:130
 travel:50</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>category,amount
 rent,500</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>rent:500</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V34" t="inlineStr">
         <is>
           <t>category,amount
 a,5
 a,5</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="W34" t="inlineStr">
         <is>
           <t>a:10</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>category,amount</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="Z34" t="inlineStr">
         <is>
           <t>category,amount
 x,0</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AA34" t="inlineStr">
         <is>
           <t>x:0</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AB34" t="inlineStr">
         <is>
           <t>category,amount
 c,-10
 c,20</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AC34" t="inlineStr">
         <is>
           <t>c:10</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AD34" t="inlineStr">
         <is>
           <t>category,amount
 z,1
@@ -6667,107 +5884,100 @@
 x,3</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AE34" t="inlineStr">
         <is>
           <t>x:3
 y:2
 z:1</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
+      <c r="AG34" t="inlineStr">
         <is>
           <t>import csv, sys
 totals = {}
-for row in csv.DictReader(sys.stdin):
+for row in csv.DictReader(sys.stdin):   # DictReader reads CSV rows as dicts
     cat = row["category"]
     totals[cat] = totals.get(cat, 0) + int(row["amount"])
-for cat in sorted(totals):
+for cat in sorted(totals):   # alphabetical order, as required
     print(f"{cat}:{totals[cat]}")</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>Python - Average per Name</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>A CSV has header 'name,score' with possibly several rows per name. Print each name's average score (rounded to 1 decimal place) as 'name:average', with names sorted alphabetically.
-### Input Format
-- Line 1: Header 'name,score'
-- Next lines: data rows
-### Output Format
-```
-asha:90.0
-kabir:60.0
-```
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>A sports coach records each athlete's score from every practice trial in a CSV, and needs a quick summary showing each athlete's average score across all their trials, listed alphabetically by name.
+A CSV has header 'name,score' with possibly several rows per name. Print each name's average score (rounded to 1 decimal place) as 'name:average', with names sorted alphabetically.
 ### Example Walkthrough
-In the sample, the rows are `asha,90` and `kabir,60`. Each name has a single score, so their averages are `90.0` and `60.0`, printed as `asha:90.0` then `kabir:60.0`.
+In the sample, `asha` has scores `80` and `100` (average `90.0`), and `kabir` has a single score `60` (average `60.0`), so the program prints `asha:90.0` then `kabir:60.0`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
         <v>5</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>file-handling</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>csv-processing</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O5" t="b">
+      <c r="O35" t="b">
         <v>0</v>
       </c>
-      <c r="P5" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="b">
-        <v>1</v>
-      </c>
-      <c r="R5" t="inlineStr">
+      <c r="P35" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q35" t="b">
+        <v>1</v>
+      </c>
+      <c r="R35" t="inlineStr">
         <is>
           <t>name,score
 asha,80
@@ -6775,24 +5985,24 @@
 kabir,60</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>asha:90.0
 kabir:60.0</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>name,score
 sam,70</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U35" t="inlineStr">
         <is>
           <t>sam:70.0</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="V35" t="inlineStr">
         <is>
           <t>name,score
 a,10
@@ -6800,24 +6010,24 @@
 a,30</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="W35" t="inlineStr">
         <is>
           <t>a:20.0
 b:20.0</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>name,score
 x,0</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Y35" t="inlineStr">
         <is>
           <t>x:0.0</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="Z35" t="inlineStr">
         <is>
           <t>name,score
 z,1
@@ -6825,12 +6035,12 @@
 z,3</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AA35" t="inlineStr">
         <is>
           <t>z:2.0</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AB35" t="inlineStr">
         <is>
           <t>name,score
 a,100
@@ -6838,114 +6048,105 @@
 c,75</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AC35" t="inlineStr">
         <is>
           <t>a:100.0
 b:50.0
 c:75.0</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AD35" t="inlineStr">
         <is>
           <t>name,score</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AG35" t="inlineStr">
         <is>
           <t>import csv, sys
 scores = {}
-for row in csv.DictReader(sys.stdin):
+for row in csv.DictReader(sys.stdin):   # DictReader reads CSV rows as dicts
     scores.setdefault(row["name"], []).append(int(row["score"]))
-for name in sorted(scores):
+for name in sorted(scores):   # alphabetical order, as required
     values = scores[name]
     print(f"{name}:{round(sum(values) / len(values), 1)}")</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>Python - Match Multiple Extensions</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Read N file names, then a line of allowed extensions separated by spaces (no dots). Print the file names whose extension is in the allowed list, in their original order.
-### Input Format
-- Line 1: N
-- Next N lines: file names
-- Last line: allowed extensions
-### Output Format
-```
-a.txt
-c.md
-d.txt
-```
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>A course-submission portal only accepts a few allowed file types, and the file-organizer app needs to filter a folder listing down to just the files whose extension is on the allowed list, keeping their original order.
+Read N file names, then a line of allowed extensions separated by spaces (no dots). Print the file names whose extension is in the allowed list, in their original order.
 ### Example Walkthrough
 In the sample, the file names are `a.txt`, `b.py`, `c.md`, and `d.txt`, and the allowed extensions are `txt` and `md`. All but `b.py` match, so the program prints `a.txt`, `c.md`, and `d.txt` in their original order.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
         <v>5</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>file-handling</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>file-paths</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O6" t="b">
+      <c r="O36" t="b">
         <v>0</v>
       </c>
-      <c r="P6" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q6" t="b">
-        <v>1</v>
-      </c>
-      <c r="R6" t="inlineStr">
+      <c r="P36" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q36" t="b">
+        <v>1</v>
+      </c>
+      <c r="R36" t="inlineStr">
         <is>
           <t>4
 a.txt
@@ -6955,14 +6156,14 @@
 txt md</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>a.txt
 c.md
 d.txt</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t>2
 x.jpg
@@ -6970,12 +6171,12 @@
 png</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>y.png</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="V36" t="inlineStr">
         <is>
           <t>3
 p.doc
@@ -6984,32 +6185,32 @@
 doc pdf</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="W36" t="inlineStr">
         <is>
           <t>p.doc
 q.pdf
 r.doc</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>0
 txt</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="Z36" t="inlineStr">
         <is>
           <t>1
 file.txt
 txt</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AA36" t="inlineStr">
         <is>
           <t>file.txt</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AB36" t="inlineStr">
         <is>
           <t>3
 a.txt
@@ -7018,7 +6219,7 @@
 py</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AD36" t="inlineStr">
         <is>
           <t>2
 a.tar.gz
@@ -7026,265 +6227,253 @@
 gz zip</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AE36" t="inlineStr">
         <is>
           <t>a.tar.gz
 b.zip</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AG36" t="inlineStr">
         <is>
           <t>from pathlib import PurePosixPath
 n = int(input())
-names = [input() for _ in range(n)]
+names = [input() for _ in range(n)]   # simulate reading a list of file names
 allowed = set(input().split())
 for name in names:
-    if PurePosixPath(name).suffix[1:] in allowed:
+    if PurePosixPath(name).suffix[1:] in allowed:   # suffix keeps the dot, so strip it before comparing
         print(name)</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>Python - Word Frequency as JSON</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Read a sentence and print a JSON object mapping each word to how many times it appears, with the keys sorted alphabetically. Use json.dumps with `sort_keys`.
-### Input Format
-- Line 1: A sentence
-### Output Format
-```
-{"a": 2, "b": 1, "c": 1}
-```
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>A vocabulary-building app scans a sentence a student is practising and exports how often each word occurs as a JSON object, so the flashcard generator can prioritise the words that repeat most.
+Read a sentence and print a JSON object mapping each word to how many times it appears, with the keys sorted alphabetically. Use json.dumps with `sort_keys`.
 ### Example Walkthrough
 In the sample, the sentence is `a b a c`. The word `a` appears `2` times and `b` and `c` appear once each, so the program prints `{"a": 2, "b": 1, "c": 1}` with keys sorted alphabetically.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
         <v>5</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>file-handling</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>json-processing</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O7" t="b">
+      <c r="O37" t="b">
         <v>0</v>
       </c>
-      <c r="P7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q7" t="b">
-        <v>1</v>
-      </c>
-      <c r="R7" t="inlineStr">
+      <c r="P37" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q37" t="b">
+        <v>1</v>
+      </c>
+      <c r="R37" t="inlineStr">
         <is>
           <t>a b a c</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S37" t="inlineStr">
         <is>
           <t>{"a": 2, "b": 1, "c": 1}</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T37" t="inlineStr">
         <is>
           <t>hello hello world</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U37" t="inlineStr">
         <is>
           <t>{"hello": 2, "world": 1}</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="V37" t="inlineStr">
         <is>
           <t>x y z</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="W37" t="inlineStr">
         <is>
           <t>{"x": 1, "y": 1, "z": 1}</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>single</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Y37" t="inlineStr">
         <is>
           <t>{"single": 1}</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="Z37" t="inlineStr">
         <is>
           <t>a a a a</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AA37" t="inlineStr">
         <is>
           <t>{"a": 4}</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AB37" t="inlineStr">
         <is>
           <t>z y x w v</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AC37" t="inlineStr">
         <is>
           <t>{"v": 1, "w": 1, "x": 1, "y": 1, "z": 1}</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AD37" t="inlineStr">
         <is>
           <t>cat dog cat bird</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AE37" t="inlineStr">
         <is>
           <t>{"bird": 1, "cat": 2, "dog": 1}</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AG37" t="inlineStr">
         <is>
           <t>import json
 words = input().split()
 counts = {}
 for w in words:
     counts[w] = counts.get(w, 0) + 1
-print(json.dumps(counts, sort_keys=True))</t>
+print(json.dumps(counts, sort_keys=True))   # write JSON the way json.dump() would write to a file</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>Python - Validate Records</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>Read N records, each 'name,age'. A record is valid only if the age is a whole number greater than 0. Print 'valid X invalid Y' with the counts of valid and invalid records.
-### Input Format
-- Line 1: N
-- Next N lines: 'name,age'
-### Output Format
-```
-valid 1 invalid 2
-```
 ### Example Walkthrough
 In the sample, the records are `asha,20` (a valid positive age), `kabir,-5` (an invalid non-positive age), and `meera,abc` (an invalid, non-numeric age). That gives `1` valid and `2` invalid records, so the program prints `valid 1 invalid 2`.
 ### Constraints
 - All numeric inputs are valid numbers in the ranges implied by the examples.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
         <v>5</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>analyze</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>file-handling</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>file-operations</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O8" t="b">
+      <c r="O38" t="b">
         <v>0</v>
       </c>
-      <c r="P8" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="b">
-        <v>1</v>
-      </c>
-      <c r="R8" t="inlineStr">
+      <c r="P38" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q38" t="b">
+        <v>1</v>
+      </c>
+      <c r="R38" t="inlineStr">
         <is>
           <t>3
 asha,20
@@ -7292,57 +6481,57 @@
 sam,abc</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S38" t="inlineStr">
         <is>
           <t>valid 1 invalid 2</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T38" t="inlineStr">
         <is>
           <t>2
 a,10
 b,30</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U38" t="inlineStr">
         <is>
           <t>valid 2 invalid 0</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V38" t="inlineStr">
         <is>
           <t>2
 x,0
 y,5</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="W38" t="inlineStr">
         <is>
           <t>valid 1 invalid 1</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Y38" t="inlineStr">
         <is>
           <t>valid 0 invalid 0</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="Z38" t="inlineStr">
         <is>
           <t>1
 zed,1</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AA38" t="inlineStr">
         <is>
           <t>valid 1 invalid 0</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AB38" t="inlineStr">
         <is>
           <t>4
 a,1
@@ -7351,154 +6540,147 @@
 d,2</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AC38" t="inlineStr">
         <is>
           <t>valid 2 invalid 2</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AD38" t="inlineStr">
         <is>
           <t>1
 p,0</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AE38" t="inlineStr">
         <is>
           <t>valid 0 invalid 1</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AG38" t="inlineStr">
         <is>
           <t>n = int(input())
 valid = invalid = 0
 for _ in range(n):
-    name, age = input().split(",")
+    name, age = input().split(",")   # simulate reading one CSV-style record per line
     try:
         if int(age) &gt; 0:
             valid += 1
         else:
             invalid += 1
-    except ValueError:
+    except ValueError:   # non-numeric age makes the record invalid
         invalid += 1
 print(f"valid {valid} invalid {invalid}")</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>Python - CSV Sum Column</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>An accounting import tool reads N rows of a CSV export where each row has an item label and an amount separated by a comma, and needs the total of just the amount column across all rows.
 Write a program that reads a whole number N, then reads N more lines each in the form `label,amount`, and prints the sum of the amount values. If N is 0, print `0`.
-### Input Format
-- Line 1: N, the number of rows
-- Next N lines: `label,amount`
-### Output Format
-```
-30
-```
 ### Example Walkthrough
 In the sample, N is 2 with rows `a,10` and `b,20`. Adding the amounts gives 10 + 20 = 30, so the program prints `30`.
 ### Constraints
 - N is a valid whole number, and every amount is a valid whole number.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
         <v>5</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>file-handling</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>csv-processing</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O9" t="b">
+      <c r="O39" t="b">
         <v>0</v>
       </c>
-      <c r="P9" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="b">
-        <v>1</v>
-      </c>
-      <c r="R9" t="inlineStr">
+      <c r="P39" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q39" t="b">
+        <v>1</v>
+      </c>
+      <c r="R39" t="inlineStr">
         <is>
           <t>2
 a,10
 b,20</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S39" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T39" t="inlineStr">
         <is>
           <t>1
 x,5</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U39" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V39" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="W39" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>3
 a,1
@@ -7506,35 +6688,35 @@
 c,3</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Y39" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="Z39" t="inlineStr">
         <is>
           <t>2
 a,-1
 b,1</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AA39" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AB39" t="inlineStr">
         <is>
           <t>1
 item,0</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AC39" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AD39" t="inlineStr">
         <is>
           <t>4
 a,10
@@ -7543,337 +6725,324 @@
 d,1</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AE39" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AG39" t="inlineStr">
         <is>
           <t>n=int(input()); total=0
-for _ in range(n): total+=int(input().split(",")[1])
+for _ in range(n): total+=int(input().split(",")[1])   # simulate reading a CSV row, taking the amount field
 print(total)</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Python - JSON List Average</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>A fitness app stores a week's daily step counts as a JSON array in a log file and needs the average steps per day to show on the weekly summary screen.
 Write a program that reads a line containing a JSON array of numbers, parses it, and prints the average of the numbers (their sum divided by how many there are).
-### Input Format
-- Line 1: A JSON array of numbers
-### Output Format
-```
-2.0
-```
 ### Example Walkthrough
 In the sample, the array is `[1,2,3]`. The average is (1 + 2 + 3) / 3 = 2.0, so the program prints `2.0`.
 ### Constraints
 - The input is a valid, non-empty JSON array of numbers.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
         <v>5</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>file-handling</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>json-processing</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O10" t="b">
+      <c r="O40" t="b">
         <v>0</v>
       </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="b">
-        <v>1</v>
-      </c>
-      <c r="R10" t="inlineStr">
+      <c r="P40" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q40" t="b">
+        <v>1</v>
+      </c>
+      <c r="R40" t="inlineStr">
         <is>
           <t>[1,2,3]</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S40" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T40" t="inlineStr">
         <is>
           <t>[5]</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U40" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V40" t="inlineStr">
         <is>
           <t>[0,10]</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="W40" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>[-1,1]</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Y40" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z40" t="inlineStr">
         <is>
           <t>[10,20,30,40]</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AA40" t="inlineStr">
         <is>
           <t>25.0</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB40" t="inlineStr">
         <is>
           <t>[0]</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AC40" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AD40" t="inlineStr">
         <is>
           <t>[100,-100,50]</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AE40" t="inlineStr">
         <is>
           <t>16.666666666666668</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AG40" t="inlineStr">
         <is>
           <t>import json
-nums=json.loads(input()); print(sum(nums)/len(nums))</t>
+nums=json.loads(input()); print(sum(nums)/len(nums))   # parse a JSON array the same way json.load() would from a file</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>Python - Missing File Guard</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>A file cleanup script checks a requested file name against the set of files that actually exist in a folder before attempting to open or delete it, to avoid a crash from trying to act on a file that isn't there.
 Write a program that reads a line of space-separated file names (the files that exist), reads one more file name on the next line, and prints `Found` if that file name is in the list, or `Missing` otherwise.
-### Input Format
-- Line 1: Space-separated file names (the files that exist)
-- Line 2: The file name being requested
-### Output Format
-```
-Found
-```
 ### Example Walkthrough
 In the sample, the existing files are `a.txt b.txt` and the requested file is `a.txt`. Since `a.txt` is in the list, the program prints `Found`.
 ### Constraints
 - The inputs are valid, non-empty lines of text.
-- Every value must be printed exactly as shown in the output format, with no extra text added or removed.</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
+- Every value must be printed exactly as expected, with no extra text added or removed.</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
         <v>5</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>apply</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>python - Set 4</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>python - Set 2</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>file-handling</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>file-errors</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="O11" t="b">
+      <c r="O41" t="b">
         <v>0</v>
       </c>
-      <c r="P11" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="b">
-        <v>1</v>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="P41" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q41" t="b">
+        <v>1</v>
+      </c>
+      <c r="R41" t="inlineStr">
         <is>
           <t>a.txt b.txt
 a.txt</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S41" t="inlineStr">
         <is>
           <t>Found</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T41" t="inlineStr">
         <is>
           <t>data.csv
 missing.csv</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U41" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V41" t="inlineStr">
         <is>
           <t>none
 a.txt</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W41" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>one two
 two</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y41" t="inlineStr">
         <is>
           <t>Found</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z41" t="inlineStr">
         <is>
           <t>README
 README</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AA41" t="inlineStr">
         <is>
           <t>Found</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB41" t="inlineStr">
         <is>
           <t>x y z
 a</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AC41" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AD41" t="inlineStr">
         <is>
           <t>report.pdf notes.doc
 notes.doc</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AE41" t="inlineStr">
         <is>
           <t>Found</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>available=set(input().split()); name=input(); print("Found" if name in available else "Missing")</t>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>available=set(input().split()); name=input(); print("Found" if name in available else "Missing")   # simulate checking a file name against a directory listing</t>
         </is>
       </c>
     </row>
